--- a/YouTube이슈분석_개인채널_2026-07-05.xlsx
+++ b/YouTube이슈분석_개인채널_2026-07-05.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="413">
   <si>
     <t>날짜</t>
   </si>
@@ -86,16 +86,16 @@
     <t>24:51</t>
   </si>
   <si>
-    <t>삼성의 지원으로 성장한 중앙그룹(JTBC)이 경영난을 겪으며 2026년 6월 206억 원의 채무불이행과 계열사 법정관리를 신청한 사건을 다룹니다. 영상은 과거 삼성과의 관계를 배신한 대가와 무리한 중계권 투자, 텐센트 자본 유치 등으로 인한 몰락 과정을 분석하며, 이로 인한 개인 투자자들의 8,000억 원대 피해 규모를 고발합니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 자극적인 제목과 허구의 미래 시점(2026년)을 가정한 클릭베이트성 콘텐츠이므로 사실관계 확인에 각별히 유의해야 합니다.</t>
+    <t>삼성이 키워준 JTBC, 은혜를 칼로 갚았습니다. 2026년 6월, JTBC가 206억 원 채무불이행을 선언하고 중앙그룹 핵심 계열사 5곳이 법정관리를 신청했습니다. 수십 년간…</t>
+  </si>
+  <si>
+    <t>자동 요약(미검수) — 원본 영상으로 내용을 확인하세요.</t>
   </si>
   <si>
     <t>▶</t>
   </si>
   <si>
-    <t>메타데이터+자막(Gemini)</t>
+    <t>메타데이터+자막(자동)</t>
   </si>
   <si>
     <t>한국 반도체에 갑질하던 애플...이젠 정반대로 중국만 보는 신세 [5분 정독]</t>
@@ -110,10 +110,7 @@
     <t>4:13</t>
   </si>
   <si>
-    <t>애플이 과거 한국 반도체 기업들에 행하던 갑질과 달리, 최근에는 공급망 다변화 실패와 중국 시장 의존도 심화로 인해 반도체 수급에 어려움을 겪고 있습니다. 삼성전자와 SK하이닉스의 위상이 높아진 가운데 애플의 전략적 변화와 향후 시장 전망을 다룹니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 제목과 달리 반도체 공급망 변화와 애플의 전략적 한계를 다루는 분석 영상이므로, 기술적 성과보다는 산업 구조적 관점에서 시청하는 것이 좋습니다.</t>
+    <t>ⓒ 무단 전재, 재배포 및 재가공, 이용(AI학습 포함)금지 협업 문의 및 제보 : video@newsis.com #반도체 #micron #삼성전자 #sk하이닉스 #애플 #ap…</t>
   </si>
   <si>
     <t>[지식뉴스] "AI 데이터센터, 이제 한국으로 몰려온다'"..빅테크가 앞다퉈 한국을 새 거점으로 점찍은 진짜 이유 (ft.조홍종 단국대 경제학과 교수) / 교양이를 부탁해</t>
@@ -128,523 +125,1135 @@
     <t>24:20</t>
   </si>
   <si>
-    <t>AI 시대의 핵심은 반도체를 넘어선 전력 확보에 있습니다. 미국이 에너지 패권을 강화하며 전력 수요가 폭증하는 가운데, 재생에너지의 간헐성과 전력망 부족 문제가 대두되고 있습니다. 한국은 우수한 전력 인프라와 원전 기술을 보유하고 있어 글로벌 데이터센터 유치의 기회를 맞이했으나, 전력망 송전 제한 및 규제 문제를 해결해야 하는 과제에 직면해 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ AI 산업의 경쟁력이 단순한 반도체 제조를 넘어 국가적인 전력 공급망과 에너지 효율성 확보에서 결정된다는 점을 주목해야 합니다.</t>
+    <t>00:00 트럼프가 노린 '에너지 패권 전쟁'의 숨겨진 속내 02:12 미국이 에너지를 장악할수록 한국·일본·대만이 더 힘든 이유 03:34 AI 패권의 진짜 병목은 반도체가 …</t>
   </si>
   <si>
     <t>재테크</t>
   </si>
   <si>
-    <t>한국 아파트 싹 다 물갈이 된다, 2027년부터 집값 무서울 겁니다 (김진 앵커 풀버전)</t>
-  </si>
-  <si>
-    <t>김작가 TV</t>
+    <t>삼전닉스 '지금부터 봐야 할 결정적 신호 3가지'ㅣ지식인 클래스 EP.06 빈센트 하나증권 애널리스트</t>
+  </si>
+  <si>
+    <t>지식인사이드</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>32:18</t>
+  </si>
+  <si>
+    <t>오늘은 하나증권 빈센트 위원 님을 모시고 삼성전자와 SK하이닉스 독주 속에서 살아남는 법과 하반기 투자 전략에 대해 들어봤습니다. 영상이 유익 했다면 구독!! 영상이 재밌으셨다…</t>
+  </si>
+  <si>
+    <t>부동산 추가 규제 나왔다, 앞으로 집값 이렇게 됩니다</t>
+  </si>
+  <si>
+    <t>부읽남TV_내집마련부터건물주까지</t>
+  </si>
+  <si>
+    <t>21:18</t>
+  </si>
+  <si>
+    <t>매주 화요일 저녁 8시 생방송 (촬영일 : 26년 6월 30일) 🎉부읽남 공식 멤버십 [바이집] 가입하기 👉 📘 『운명을 바꾸는 부동산 투자수업』  부동산 추가 규제 나왔다, …</t>
+  </si>
+  <si>
+    <t>삼성전자 SK하이닉스주식 꽉 잡으세요. 조만간 정말 무서울 겁니다. ( 조진표 대표 )</t>
+  </si>
+  <si>
+    <t>경제 원탑</t>
+  </si>
+  <si>
+    <t>36:27</t>
+  </si>
+  <si>
+    <t>삼성전자 SK하이닉스주식 꽉 잡으세요. 조만간 정말 무서울 겁니다. ( 조진표 대표 ) 📌 조진표 대표의 무료특강 신청 링크 👉  📌《조진표 대표의 주식투자 불패의 법칙》 도서…</t>
+  </si>
+  <si>
+    <t>자기계발</t>
+  </si>
+  <si>
+    <t>허경환이랑 프랑스 여행 계획 짜기 1일차 (파리민수, 영어공부법, 고민상담)</t>
+  </si>
+  <si>
+    <t>악성 내성인 정일영</t>
+  </si>
+  <si>
+    <t>19:31</t>
+  </si>
+  <si>
+    <t>일영쌤의 고민 파괴는 오늘도 계속됩니다. 🔥악성 내성인 정일영🔥 스타를 꿈꾸는 65세 정일영의 데뷔 여정기 매주 수요일 저녁 6시 30분 #정일영 #악성내성인정일영 #허경환 =…</t>
+  </si>
+  <si>
+    <t>[효과보장] 고대생이 알려주는 국어 시간 단축법 세가지 外 多</t>
+  </si>
+  <si>
+    <t>이채연</t>
+  </si>
+  <si>
+    <t>17:07</t>
+  </si>
+  <si>
+    <t>안녕하세요! 드디어 공부법 2편 영상입니다 ㅎㅎ 1편도 보고 오시는걸 추천드립니다!! 다음 영상은 마이린이랑 동묘에서 산 재료들로 액괴 만들기 대결한 영상이 올라갈 것 같습니다…</t>
+  </si>
+  <si>
+    <t>헬스터디 이채연이 알려주는 국어 공부법</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>오늘은 국어 공부법 영상!!! 이번 주 주말 중으로 2탄 바로 올릴게용 궁금한점은 댓글로! 비즈니스 메일 : lcyeoon@fromyou.co.kr #공부법 #국어공부법 #수능…</t>
+  </si>
+  <si>
+    <t>게임</t>
+  </si>
+  <si>
+    <t>혜안져스 "메차 카멜레온" 이제 쥰내 잘합니다ㅋㅋㅋㅋㅋㅋ🔥</t>
+  </si>
+  <si>
+    <t>혜안</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>29:49</t>
+  </si>
+  <si>
+    <t>숨꼭져스2 [업로드] 금,토,일,월 [문의메일] zxcv34276@gmail.com [인스타그램] @hxxax_ #혜안 #메챠카멜레온 Music provided by 브금대통령…</t>
+  </si>
+  <si>
+    <t>랄로 마스터 갔다</t>
+  </si>
+  <si>
+    <t>랄로</t>
+  </si>
+  <si>
+    <t>35:47</t>
+  </si>
+  <si>
+    <t>랄로 풀코스 youtube.com/@랄롱 치지직 생방송  각종 비지니스 aba060847@gmail.com</t>
+  </si>
+  <si>
+    <t>잠뜰 TV 콘텐츠 속 최악의 생존 난이도 1위 세계관은?</t>
+  </si>
+  <si>
+    <t>잠뜰 TV</t>
+  </si>
+  <si>
+    <t>1:18:28</t>
+  </si>
+  <si>
+    <t>수많은 잠뜰 TV 세계관 중 어떤 세계관이 가장 살기 힘들까😏 ▶구독하기❤&amp; 좋아요👍버튼을 눌러주세요! 큰 힘이 됩니다 :D ----------------------------…</t>
+  </si>
+  <si>
+    <t>IT·테크</t>
+  </si>
+  <si>
+    <t>고프로 망한 거 아니었나요? 2년만에 칼을 갈고 내놓은 신작 사봤습니다.....</t>
+  </si>
+  <si>
+    <t>ITSub잇섭</t>
+  </si>
+  <si>
+    <t>13:39</t>
+  </si>
+  <si>
+    <t>액션캠을 떠올리면 당연히 생각나는 브랜드. 고프로가 있죠. 고프로는 아주 오래전부터 여러가지 시리즈를 출시하며 엄청난 인기를 얻어왔는데요, 최근 몇년 사이 DJI, insta3…</t>
+  </si>
+  <si>
+    <t>요즘 13만원짜리 게임기 RG 로테이트 수준</t>
+  </si>
+  <si>
+    <t>UNDERkg</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>- 자세한 사진은  - 아니 글쎄 안드로이드 기반의 게임기인데 90도 화면이 돌아가면서 게임패드가 나와요. 그러면서 $87 정도라서 가격도 나름 합리적. 써 보니까 인터페이스도…</t>
+  </si>
+  <si>
+    <t>플레이스토어가 나를 감시한다고? 갤럭시폰에서  ‘이 버튼’ 당장 끄고 개인정보와 스마트폰 배터리 둘 다 잡으세요!</t>
+  </si>
+  <si>
+    <t>시니어정보 양쌤</t>
+  </si>
+  <si>
+    <t>2026-06-06</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>스마트폰이 이상하게 빨리 뜨거워지고 배터리가 금방 닳는 이유가 궁금하셨나요? 내 휴대폰이 나도 모르는 사이에 어떤 정보를 보내고 있는지 걱정되셨나요? 이번 영상에서는 갤럭시 스…</t>
+  </si>
+  <si>
+    <t>라이프</t>
+  </si>
+  <si>
+    <t>일본 오사카에서 어깨빵하는 빌런 참교육 하는 육은영쌤</t>
+  </si>
+  <si>
+    <t>매드브로 MadBros</t>
+  </si>
+  <si>
+    <t>15:16</t>
+  </si>
+  <si>
+    <t>냉각 기능을 켜면 차가워지는 요즘 유행하는 냉각 손선풍기! 56%할인율 적용 #매드브로 #육은영 #쓰줍맨 #육은영쌤의동네한바퀴 #육은영쌤 #동네한바퀴 #육퀴즈 #참교육</t>
+  </si>
+  <si>
+    <t>100시간 동안 세계에서 가장 오염된 도시에서 살면 생기는 일</t>
+  </si>
+  <si>
+    <t>고재영</t>
   </si>
   <si>
     <t>2026-06-28</t>
   </si>
   <si>
-    <t>1:28:28</t>
-  </si>
-  <si>
-    <t>김진 앵커가 출연하여 한국 주식 시장의 위기 상황과 향후 아파트 시장의 변화를 예측합니다. 특히 2027년 이후 한국 아파트 시장의 대대적인 변화를 예고하며, 투자자들이 현금 보유보다 유망한 자산 두 가지로 이동해야 할 필요성을 강조하는 경제 전망 콘텐츠입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 문구로 공포심을 유발하여 시청을 유도하는 클릭베이트 성격이 강하므로, 구체적인 투자 결정을 내리기 전 반드시 공신력 있는 자료를 통해 직접 검증하시기 바랍니다.</t>
-  </si>
-  <si>
-    <t>진짜 확실한 매도 타이밍, "차트 말고 '이걸' 봐야 합니다"ㅣ지식인 클래스 EP.07 빈센트 하나증권 애널리스트</t>
-  </si>
-  <si>
-    <t>지식인사이드</t>
-  </si>
-  <si>
-    <t>2026-07-02</t>
-  </si>
-  <si>
-    <t>25:03</t>
-  </si>
-  <si>
-    <t>빈센트 애널리스트가 출연하여 주식 투자 전략과 반도체 시장을 분석합니다. 장기 투자의 본질과 금리 공포에 대응하는 법을 다루며, 특히 삼성전자와 SK하이닉스 등 주도주의 매도 타이밍을 판단하는 핵심 기준과 좋은 기업을 주식으로 고를 때 주의해야 할 요소를 실전 관점에서 상세히 설명합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 주가 차트만 보지 말고 기업의 실적과 산업 사이클의 본질을 파악하여 매도 타이밍을 결정하는 것이 중요합니다.</t>
-  </si>
-  <si>
-    <t>반도체에 무슨 일이 생긴 거야? [코너별 다시보기 - 260702]</t>
-  </si>
-  <si>
-    <t>[팟빵] 최욱의 매불쇼</t>
-  </si>
-  <si>
-    <t>38:38</t>
-  </si>
-  <si>
-    <t>최욱의 매불쇼 경제 코너에서 박시동, 박근형 패널이 출연하여 최근 반도체 시장의 변동성과 주가 흐름을 심층 분석했습니다. 글로벌 반도체 산업을 둘러싼 이슈와 투자자들이 주목해야 할 시장의 변화를 경제 전문가의 시각에서 명쾌하게 짚어주며 투자자들에게 인사이트를 제공합니다.</t>
-  </si>
-  <si>
-    <t>최신 경제 이슈를 다루는 전문가들의 분석을 통해 반도체 관련 투자 전략을 수립하는 데 참고할 수 있습니다.</t>
-  </si>
-  <si>
-    <t>자기계발</t>
-  </si>
-  <si>
-    <t>이렇게 생각하기 시작하면 인생이 갑자기 잘 풀립니다 (자기 관리 편)</t>
-  </si>
-  <si>
-    <t>한창수의 마음정비소</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>본 영상은 한창수 교수가 출연하여 현대인의 불안과 불행의 근본적인 원인을 심리학적 관점에서 분석합니다. 외부 환경보다 자신의 내면을 들여다보는 과정이 중요함을 강조하며, 불안의 실체를 파악하고 마음을 정비함으로써 인생의 난관을 빠르게 해결할 수 있는 실질적인 마음 챙김의 비법을 제시합니다.</t>
-  </si>
-  <si>
-    <t>불안의 감정이 느껴질 때 그 원인을 막연히 피하지 말고, 자신의 내면을 구체적으로 직면하는 것만으로도 마음의 안정을 찾을 수 있습니다.</t>
-  </si>
-  <si>
-    <t>게임</t>
-  </si>
-  <si>
-    <t>혜안져스 "메차 카멜레온" 이제 쥰내 잘합니다ㅋㅋㅋㅋㅋㅋ🔥</t>
-  </si>
-  <si>
-    <t>혜안</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>29:49</t>
-  </si>
-  <si>
-    <t>유튜버 혜안이 메타버스 플랫폼 내 인기 콘텐츠인 '메차 카멜레온' 게임을 플레이하는 영상입니다. 초반에는 서툰 모습을 보였으나, 점차 게임의 규칙과 요령을 완벽하게 익히며 놀라운 실력을 보여주는 과정을 담고 있습니다. 특유의 입담과 긴장감 넘치는 추격전이 재미 요소입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 클릭베이트 성격의 제목이나 영상의 핵심은 단순한 실력 향상이 아닌 혜안 특유의 예능감 넘치는 게임 플레이 과정을 즐기는 것에 있습니다.</t>
-  </si>
-  <si>
-    <t>랄로 마스터 갔다</t>
-  </si>
-  <si>
-    <t>랄로</t>
-  </si>
-  <si>
-    <t>35:47</t>
-  </si>
-  <si>
-    <t>유튜버 랄로가 리그 오브 레전드에서 오랜 노력 끝에 마스터 티어에 달성하는 과정을 담은 영상입니다. 특유의 입담과 함께 고난도 게임 플레이를 선보이며, 시청자들에게 마스터 티어 진입이라는 성취의 순간을 공유하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 썸네일과 제목으로 시청자의 호기심을 유발하는 랄로의 방송 스타일을 엿볼 수 있습니다.</t>
-  </si>
-  <si>
-    <t>잠뜰 TV 콘텐츠 속 최악의 생존 난이도 1위 세계관은?</t>
-  </si>
-  <si>
-    <t>잠뜰 TV</t>
-  </si>
-  <si>
-    <t>1:18:28</t>
-  </si>
-  <si>
-    <t>본 영상은 잠뜰 TV가 제작한 수많은 마인크래프트 콘텐츠 세계관 중, 가장 생존 난이도가 높은 세계관이 무엇인지 분석하고 순위를 매기는 내용을 담고 있습니다. 각 세계관의 독특한 설정과 환경적 제약, 위협 요소를 고려하여 어떤 세계가 가장 혹독한 환경인지 시청자들과 함께 흥미롭게 다루고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 클릭베이트 성격이 강한 콘텐츠이므로, 각 세계관의 상세한 난이도 기준보다는 출연진의 주관적 평가와 재미 요소에 집중하여 시청하시는 것을 권장합니다.</t>
-  </si>
-  <si>
-    <t>IT·테크</t>
-  </si>
-  <si>
-    <t>긴급속보 | 애플, 최소 20만원 넘게 가격 올려버렸다? 갑자기 이런 미친 결정을 한 진짜 이유</t>
-  </si>
-  <si>
-    <t>ITSub잇섭</t>
+    <t>45:14</t>
+  </si>
+  <si>
+    <t>인스타 :  이메일 : gojaeyoungbusiness@gmail.com 비하인드 : @gojaeyoung_sub</t>
+  </si>
+  <si>
+    <t>아들이랑 둘이사는 서인영 절친 싱글맘 조민아 집 최초공개 (+오해와 진실)</t>
+  </si>
+  <si>
+    <t>개과천선 서인영</t>
+  </si>
+  <si>
+    <t>29:23</t>
+  </si>
+  <si>
+    <t>안녕하세요 여러부운~ 오늘은 저의 친구이자 소중한 멤버 민아집에 놀라갔습니다~ 민아랑 긴 시간동안 풀지못했던 오해들이 있었지만 막상 마주하니 그 시간이 무색해 질만큼 너무 편하…</t>
+  </si>
+  <si>
+    <t>일본</t>
+  </si>
+  <si>
+    <t>【元テレ東×元朝日新聞対談】新聞とテレビは終わるのか？朝日毎日読売の生存戦略／ネット時代の「有料課金」は日経一人勝ちか？／AI時代求められるのは「誰が言っているか」【下矢一良×今野忍】｜選挙ドットコム</t>
+  </si>
+  <si>
+    <t>選挙ドットコムちゃんねる</t>
+  </si>
+  <si>
+    <t>1:03:15</t>
+  </si>
+  <si>
+    <t>【ポスト田﨑史郎氏は今野忍記者！？／PRのプロに聞く！日本のメディア、どうすれば生き残れますか？？】 今回はPR戦略コンサルタントの下矢一良さんにインタビューを行いました！ 政治記者の今野忍さんを…</t>
+  </si>
+  <si>
+    <t>【必見】50代以降は月10万円の積立投資だけで老後人生が激変します！</t>
+  </si>
+  <si>
+    <t>『資産保全学』50,60代の賢い資産の守り方</t>
+  </si>
+  <si>
+    <t>38:41</t>
+  </si>
+  <si>
+    <t>【僕とLINEでつながりませんか？】 YouTubeでは話せない裏側の情報や お友達限定動画をLINEで配信中していきます！！！ ↓分部彰吾とつながる↓  ◆━━━━━━━━━━━━━━━━━━◆…</t>
+  </si>
+  <si>
+    <t>【元手200万→10億円】キオクシアだけを見るな！次の注目はTOPIX？／新NISA「最初の3000万円」がカギ／億を目指す4つの投資方法《上岡正明》</t>
+  </si>
+  <si>
+    <t>楽待 RAKUMACHI</t>
+  </si>
+  <si>
+    <t>53:57</t>
+  </si>
+  <si>
+    <t>▼不動産投資なら、収益物件数NO.1「楽待アプリ」▼  ▼上岡正明さんのYouTubeチャンネルはこちら▼  ▼おすすめの関連動画はこちら▼    ▼さらに実践的で役立つ動画を配信中！▼ 「楽待プ…</t>
+  </si>
+  <si>
+    <t>金利上昇でどんな影響が起こるのか…2026年後半の株式市場と投資家の明暗</t>
+  </si>
+  <si>
+    <t>ほったらかし投資のフクロウ先生</t>
+  </si>
+  <si>
+    <t>32:40</t>
+  </si>
+  <si>
+    <t>今回の動画は、「利上げ＝株安」のウソというテーマで、歴史に学ぶ2026年後半の相場と長期投資家がやるべきことについてお話ししました。 今この局面で、長期投資家がやるべき4つのこととは何か？ 是非最…</t>
+  </si>
+  <si>
+    <t>【受験の天王山が始まる...】前に必ず見てほしい高3向け"7月の勉強法"を解説します。</t>
+  </si>
+  <si>
+    <t>河野塾チャンネル</t>
+  </si>
+  <si>
+    <t>6:16</t>
+  </si>
+  <si>
+    <t>📝2026年度 第1回共通テスト型KONO模試の受験はこちらから！  【第1回共通テスト型KONO模試 概要】 対象学年：中学生・高校生・既卒生・その他 受験料：無料 受付期間：6/13(土)0:…</t>
+  </si>
+  <si>
+    <t>7月で圧倒的に成績が伸びる勉強法 TOP5</t>
+  </si>
+  <si>
+    <t>ブレイクスルー佐々木</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>7:34</t>
+  </si>
+  <si>
+    <t>プロモーション：東進ハイスクール・東進衛星予備校 東進の夏期特別招待講習 申し込み受付中！  ◆受講資格 志望校合格を目指して学習に取り組む、意欲ある高3生・高2生・高1生(東進生でない方)/高0…</t>
+  </si>
+  <si>
+    <t>음악</t>
+  </si>
+  <si>
+    <t>「瞬間ジャーニー」 Music Video ／ TOP4(キヨ・レトルト・牛沢・ガッチマン)</t>
+  </si>
+  <si>
+    <t>キヨ。</t>
   </si>
   <si>
     <t>2026-06-26</t>
   </si>
   <si>
+    <t>3:49</t>
+  </si>
+  <si>
+    <t>一瞬は永遠の宝物 「瞬間ジャーニー」 Music Video／TOP4(キヨ・レトルト・牛沢・ガッチマン) 作詞：HIROKI(ORANGE RANGE) 作曲：NAOTO(ORANGE RANG…</t>
+  </si>
+  <si>
+    <t>IS:SUE (イッシュ) 'come again' (Original by m-flo) Live Performance [2026.06.19 REBORN Collection 2026]</t>
+  </si>
+  <si>
+    <t>IS:SUE</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>5:04</t>
+  </si>
+  <si>
+    <t>IS:SUE (イッシュ) 'come again' (Original by m-flo) Live Performance [2026.06.19 REBORN Collection 2026…</t>
+  </si>
+  <si>
+    <t>【マインクラフト】地下の強制労働施設で埋蔵金を探すことになりました【日常組】</t>
+  </si>
+  <si>
+    <t>日常組</t>
+  </si>
+  <si>
+    <t>1:34:58</t>
+  </si>
+  <si>
+    <t>面白かったら高評価してやって下さい！ 制作者：るーぷ様  俺たち日常組の公式サイトが出来ました!→ チャンネル登録→ follow me!→ 日常メンバー ぺいんと: しにがみ: クロノア: トラ…</t>
+  </si>
+  <si>
+    <t>【DbD】結月ゆかりの逃走劇：狂乱の宴編【VOICEROID実況】</t>
+  </si>
+  <si>
+    <t>すき焼き大好きTV</t>
+  </si>
+  <si>
+    <t>27:43</t>
+  </si>
+  <si>
+    <t>初投稿です。 【次回】→ 近日公開 【前回】→  〇Twitter:  【動画クレジット】 〇立ち絵提供：ノヤマコト様 ・Twitter:  ・pixiv:  ・youtube:  〇EDテーマ …</t>
+  </si>
+  <si>
+    <t>【超豪華】今夜限りのW杯日本代表チームとのカスタムが大波乱で激熱すぎたｗｗ【VALORANT / ヴァロラント】</t>
+  </si>
+  <si>
+    <t>GON</t>
+  </si>
+  <si>
+    <t>37:14</t>
+  </si>
+  <si>
+    <t>前回⇒ 次回⇒ 高評価・チャンネル登録・ハイプ 是非 ここで配信中！    ⚡初めてGONを知った人におすすめの動画┃ スプラトゥーン：  ホラーゲーム：  単発動画シリーズ：  GONvs視聴者…</t>
+  </si>
+  <si>
+    <t>【今すぐオフ】Googleアカウントの新しいプライバシー設定と3つの変更点をわかりやすく解説！【2026年6月～】</t>
+  </si>
+  <si>
+    <t>スマホのコンシェルジュ「株式会社コアコンシェル」</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>9:20</t>
+  </si>
+  <si>
+    <t>今回は、6月はじめにGoogleから届いた謎のメールについて解説します。 動画前半では今回の変更点について、また後半では設定を見直すべきポイントについても解説しますので、是非最後までチェックしてみ…</t>
+  </si>
+  <si>
+    <t>【ボロ儲け】18万円→2万5000円！！ジャンク品から発掘したプロ専用ボードがお宝だった</t>
+  </si>
+  <si>
+    <t>おじおじの穴</t>
+  </si>
+  <si>
+    <t>32:03</t>
+  </si>
+  <si>
+    <t>#JLCPCB 新規ユーザーの方は$123クーポンが貰えます！いますぐリンクに飛んで取得しよう！  メインチャンネル↓  楽曲提供：NoCopyrightSounds（NCS） URL： NCS …</t>
+  </si>
+  <si>
+    <t>【ルームツアー?】自宅にクソでかサーバーを作ったYouTuberがいるらしいので調査してきました。</t>
+  </si>
+  <si>
+    <t>TECH WORLD</t>
+  </si>
+  <si>
+    <t>25:48</t>
+  </si>
+  <si>
+    <t>うんちゃまさんのチャンネル @unchama 今回はうんちゃまさんの自宅サーバーにお邪魔しました。「そういえばおれ自宅にサーバー置いてないかも」という方に是非見ていただきたいです。 【チャンネルス…</t>
+  </si>
+  <si>
+    <t>溝口さんに「それ違います」と正直に伝えました</t>
+  </si>
+  <si>
+    <t>ヤマト リノ 本物</t>
+  </si>
+  <si>
+    <t>1:05:52</t>
+  </si>
+  <si>
+    <t>ヤマトリノです。 10万人のメインチャンネル乗っ取られて、戻らないかもしれないので新しくチャネル作りました。 絶対チャンネル登録お願いします😭 ▫️インスタ  ▫️X  📩お仕事の相談はこちらから…</t>
+  </si>
+  <si>
+    <t>【石川県金沢】酔った勢いで旅行したら、過去最悪の空気の旅行が仕上がりました。</t>
+  </si>
+  <si>
+    <t>うじとうえだ</t>
+  </si>
+  <si>
+    <t>2:18:07</t>
+  </si>
+  <si>
+    <t>★過去の徹夜で国内旅企画はこちら！ （名古屋） （仙台） （栃木） （京都） （茨城） （群馬） ★前回の酒鬱状態の氏原  【氏原】（メガネ金髪） 38歳の元芸人「ブチギレ氏原」、社員4人の会社の…</t>
+  </si>
+  <si>
+    <t>미국</t>
+  </si>
+  <si>
+    <t>China Just Shut Down Gold Trading</t>
+  </si>
+  <si>
+    <t>Andrei Jikh</t>
+  </si>
+  <si>
+    <t>25:32</t>
+  </si>
+  <si>
+    <t>China Will Launch A New Gold System (July 24th) ► Alpha Picks:  Bundle:  Premium:  ► Premium Membe…</t>
+  </si>
+  <si>
+    <t>I Finally Snapped | Financial Audit</t>
+  </si>
+  <si>
+    <t>Caleb Hammer</t>
+  </si>
+  <si>
+    <t>1:42:30</t>
+  </si>
+  <si>
+    <t>*AGHHHHH SHE NEVER PAYS HER TAXES!!!*In the post show, we learn she refuses to pay taxes. She want…</t>
+  </si>
+  <si>
+    <t>The Most INSANE Couple Ever | Financial Audit</t>
+  </si>
+  <si>
+    <t>1:41:16</t>
+  </si>
+  <si>
+    <t>Your data is being sold right now. My sponsor Aura will find the brokers selling it and remove you…</t>
+  </si>
+  <si>
+    <t>Boys Life || Roni Raman || Mehnat Ka Raja || Rohit Raman  || Motivational New Haryanvi Song 2026</t>
+  </si>
+  <si>
+    <t>Roni Raman Official</t>
+  </si>
+  <si>
+    <t>6:26</t>
+  </si>
+  <si>
+    <t>RONI RAMAN PRESENTS LATEST NEW HARYANVI SONG 2025 🌍 🎵 “ Boys Life ” BRAND NEW HARYANVI 🎶 🗣️SONG IN…</t>
+  </si>
+  <si>
+    <t>बाप की पगड़ी पार्ट-48 ।। A Motivation Short Film।। Marwadi Masti</t>
+  </si>
+  <si>
+    <t>राजू कबाड़ी</t>
+  </si>
+  <si>
+    <t>24:26</t>
+  </si>
+  <si>
+    <t>बाप की पगड़ी पार्ट-48 ।। A Motivation Short Film।। Marwadi Masti #marwadi_masti #kakakajodkicomedy…</t>
+  </si>
+  <si>
+    <t>SBI PO + IBPS PO July 2026 Study Plan: What to Study Daily | Aashish Arora</t>
+  </si>
+  <si>
+    <t>Studified</t>
+  </si>
+  <si>
+    <t>13:32</t>
+  </si>
+  <si>
+    <t>For New Students, Who want to get AASHISH ARORA QUANT SUBSCRIPTION, LINK:  CODE: TT60 For New Stud…</t>
+  </si>
+  <si>
+    <t>32. Cutie Mew Mew Magic (DELTARUNE Chapter 5 Soundtrack) - Toby Fox &amp; @Cametek.CamelliaOfficial</t>
+  </si>
+  <si>
+    <t>Toby Fox</t>
+  </si>
+  <si>
+    <t>3:05</t>
+  </si>
+  <si>
+    <t>Listen elsewhere:  Full credits:  Acceptable usage guidelines and licensing:  #DELTARUNE #TobyFox …</t>
+  </si>
+  <si>
+    <t>GloRilla &amp; Pooh Shiesty - MANE (Official Visual)</t>
+  </si>
+  <si>
+    <t>theofficialGloRilla</t>
+  </si>
+  <si>
+    <t>3:08</t>
+  </si>
+  <si>
+    <t>Listen to Glorilla’s and Pooh Shiesty’s “MANE” out now:  Follow #GloRilla: Instagram:  Twitter:  T…</t>
+  </si>
+  <si>
+    <t>34. Flower Man (DELTARUNE Chapter 5 Soundtrack) - Toby Fox &amp; @Cametek.CamelliaOfficial</t>
+  </si>
+  <si>
+    <t>3:13</t>
+  </si>
+  <si>
+    <t>10 YouTubers vs 2 Secret Traitors</t>
+  </si>
+  <si>
+    <t>MrBeast Gaming</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>I can't believe how this ended Go get yourself some Feastables peanut butter cups 👉  New Merch -  …</t>
+  </si>
+  <si>
+    <t>I Got Trained By a Minecraft Combat Master</t>
+  </si>
+  <si>
+    <t>FlameFrags</t>
+  </si>
+  <si>
+    <t>36:19</t>
+  </si>
+  <si>
+    <t>I Got Trained by the God of War Unstable SMP: ➜ @wemmbumc ➜ @ParrotX2 ➜ @Spokeishere ➜ @FlameFrags…</t>
+  </si>
+  <si>
+    <t>ALL THE SIDEMEN FINALLY PLAY MECCHA CHAMELEON</t>
+  </si>
+  <si>
+    <t>MoreSidemen</t>
+  </si>
+  <si>
+    <t>27:16</t>
+  </si>
+  <si>
+    <t>🎥 Watch Side+ FREE with 3-Day Free Trial:  🍗: Order food NOW at:  🍹: XIX Vodka:  👉🏻: Subscribe to …</t>
+  </si>
+  <si>
+    <t>스포츠</t>
+  </si>
+  <si>
+    <t>Argentina vs Cape Verde Highlights 🌎🏆 2026 FIFA World Cup™ | Round of 32</t>
+  </si>
+  <si>
+    <t>FOX Sports</t>
+  </si>
+  <si>
+    <t>26:13</t>
+  </si>
+  <si>
+    <t>Check out the full game highlights between Argentina and Cape Verde in the 2026 FIFA World Cup™. A…</t>
+  </si>
+  <si>
+    <t>Who Gets Eliminated? (YGT Round 2)</t>
+  </si>
+  <si>
+    <t>Bryan Bros Golf</t>
+  </si>
+  <si>
+    <t>3:48:37</t>
+  </si>
+  <si>
+    <t>Your Golf Tour 2026 Episode 2 - the start of true competitive golf on YouTube. Grant Horvat, Georg…</t>
+  </si>
+  <si>
+    <t>I Hate Modern Desks... So I Built This.</t>
+  </si>
+  <si>
+    <t>Morley Kert</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>28:49</t>
+  </si>
+  <si>
+    <t>Building my dream desk. Thank you Opera for sponsoring this video! Try Opera for free:  Behind the…</t>
+  </si>
+  <si>
+    <t>My First 17 Minutes With the Steam Machine</t>
+  </si>
+  <si>
+    <t>ShortCircuit</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>20:23</t>
+  </si>
+  <si>
+    <t>Pre-order your Companion Cube at  The Steam Machine is finally here! Linus gets his hands on the f…</t>
+  </si>
+  <si>
+    <t>Clicks Communicator: First Look</t>
+  </si>
+  <si>
+    <t>Clicks</t>
+  </si>
+  <si>
+    <t>After thousands of hours, hundreds of decisions and sweating every tiny detail, the first hands-on…</t>
+  </si>
+  <si>
+    <t>영국</t>
+  </si>
+  <si>
+    <t>Will Farage's Extreme Wealth Be His Downfall?</t>
+  </si>
+  <si>
+    <t>The Rest Is Politics</t>
+  </si>
+  <si>
+    <t>48:08</t>
+  </si>
+  <si>
+    <t>Watch AD FREE here:  How has Farage become the highest earning MP, while still claiming to be “for…</t>
+  </si>
+  <si>
+    <t>This stock has more potential upside than anything I have seen‼️</t>
+  </si>
+  <si>
+    <t>Jeremy Lefebvre Makes Money</t>
+  </si>
+  <si>
+    <t>39:04</t>
+  </si>
+  <si>
+    <t>1000x 4th of July sale sign up  ✅ Want in? Join My Private Stock &amp; Wealth Group &amp; Get Access to 10…</t>
+  </si>
+  <si>
+    <t>🟡 బంగారం అమ్మడానికి Queue కడుతున్నారు</t>
+  </si>
+  <si>
+    <t>Money Purse { మనీ పర్స్ }</t>
+  </si>
+  <si>
+    <t>21:39</t>
+  </si>
+  <si>
+    <t>Buy 11 Stock Investing Strategies Book👉  Get 20% discount Using Coupon Cone: MONEY20 Our SEBI Regi…</t>
+  </si>
+  <si>
+    <t>The Power of 4 AM - सुबह जल्दी उठकर देखो ज़िंदगी बदल जाएगी | Life Changing Story</t>
+  </si>
+  <si>
+    <t>Udaan Stories</t>
+  </si>
+  <si>
+    <t>8:15</t>
+  </si>
+  <si>
+    <t>The Power of 4 AM - सुबह जल्दी उठकर देखो ज़िंदगी बदल जाएगी | Life Changing Story क्या सिर्फ सुबह 4…</t>
+  </si>
+  <si>
+    <t>👉 నువ్వు ఒకరి దగ్గర తగ్గకుండా ఉండాలంటే ఈ 4 సూత్రాలు గుర్తుపెట్టుకో | 4 Rules to Increase Your Value</t>
+  </si>
+  <si>
+    <t>Voice Of Nalini</t>
+  </si>
+  <si>
+    <t>9:50</t>
+  </si>
+  <si>
+    <t>నిన్ను ఎవరూ గౌరవించడం లేదని ఎప్పుడైనా అనిపించిందా? లేదా కొందరు నిన్ను తక్కువగా చూస్తున్నారని బాధపడ…</t>
+  </si>
+  <si>
+    <t>Comment le Maroc a PUNI l'arrogance des Pays-Bas</t>
+  </si>
+  <si>
+    <t>H5 Motivation</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>Coupe du monde 2026 : le Maroc renverse les Pays-Bas et décroche sa qualification pour les 8es de …</t>
+  </si>
+  <si>
+    <t>Sprint Highlights | 2026 British Grand Prix</t>
+  </si>
+  <si>
+    <t>FORMULA 1</t>
+  </si>
+  <si>
+    <t>8:10</t>
+  </si>
+  <si>
+    <t>With battles from lights to flag, catch up on an action-packed Sprint at the British Grand Prix! F…</t>
+  </si>
+  <si>
+    <t>SIDEMEN 100 MYSTERY GOALS BUT ONLY ONE ENDS THE VIDEO</t>
+  </si>
+  <si>
+    <t>Sidemen</t>
+  </si>
+  <si>
+    <t>1:15:17</t>
+  </si>
+  <si>
+    <t>🎥 Watch Side+ FREE with 3-Day Free Trial -  🍗 Order food NOW at:  🍹 XIX Vodka:  👕 Sidemen Clothing…</t>
+  </si>
+  <si>
+    <t>Antigravity A1: A New Take on Drones!</t>
+  </si>
+  <si>
+    <t>Marques Brownlee</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>Thanks Antigravity for sponsoring this video! Get 25% off the A1 at  for a limited time, and get 2…</t>
+  </si>
+  <si>
+    <t>독일</t>
+  </si>
+  <si>
+    <t>Erfurt eskaliert: Antifant will mich angreifen und kassiert Ansage!</t>
+  </si>
+  <si>
+    <t>Aktien mit Kopf</t>
+  </si>
+  <si>
     <t>12:18</t>
   </si>
   <si>
-    <t>ITSub잇섭 채널이 2026년 6월 25일 기습적으로 발표된 애플의 전방위적인 가격 인상 소식을 다룹니다. 기존 제품군 가격이 최대 54.3%까지 급등한 현황을 분석하고, 메모리 공급난 등 복합적인 인상 배경과 한국 시장의 중요성 및 CEO들의 방한 이유를 심도 있게 고찰합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 갑작스러운 가격 인상 뉴스에 현혹되기보다 애플의 공급망 정책 변화와 환율 및 메모리 시장 상황을 종합적으로 파악하는 안목이 필요합니다.</t>
-  </si>
-  <si>
-    <t>요즘 13만원짜리 게임기 RG 로테이트 수준</t>
-  </si>
-  <si>
-    <t>UNDERkg</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>안드로이드 기반의 13만 원대 게임기 'RG 로테이트'에 대한 리뷰입니다. 기기 화면이 90도로 회전하며 게임패드가 나타나는 독특한 설계가 특징이며, 조작감과 인터페이스가 가격 대비 준수한 편입니다. 다만 L2, R2 버튼의 조작성과 진동 모터 위치, 조도 센서 부재 등 몇 가지 아쉬운 점이 있으나 전반적으로 가격 대비 만족도가 높은 기기입니다.</t>
-  </si>
-  <si>
-    <t>해당 기기는 13만 원대의 저렴한 가격에 독특한 폼팩터를 경험할 수 있으나, L2/R2 버튼의 조작 편의성을 반드시 고려해야 합니다.</t>
-  </si>
-  <si>
-    <t>플레이스토어가 나를 감시한다고? 갤럭시폰에서  ‘이 버튼’ 당장 끄고 개인정보와 스마트폰 배터리 둘 다 잡으세요!</t>
-  </si>
-  <si>
-    <t>시니어정보 양쌤</t>
-  </si>
-  <si>
-    <t>2026-06-06</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>본 영상은 갤럭시 스마트폰 사용자를 위해 배터리 소모를 줄이고 개인정보 보호를 강화하는 필수 설정법을 안내합니다. 구글 플레이스토어의 데이터 전송 차단, 위치 정보 및 진단 데이터 전송 해제, 안드로이드 맞춤형 서비스 중지 등 실질적인 스마트폰 최적화 방법을 화면을 통해 쉽고 상세하게 설명하여 초보자도 바로 따라 할 수 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 모든 설정을 한꺼번에 바꾸기 어렵다면, 배터리 소모가 가장 심한 위치 정보와 진단 데이터 전송 설정부터 먼저 확인해 보세요.</t>
-  </si>
-  <si>
-    <t>라이프</t>
-  </si>
-  <si>
-    <t>일본 오사카에서 어깨빵하는 빌런 참교육 하는 육은영쌤</t>
-  </si>
-  <si>
-    <t>매드브로 MadBros</t>
-  </si>
-  <si>
-    <t>2026-07-01</t>
-  </si>
-  <si>
-    <t>15:16</t>
-  </si>
-  <si>
-    <t>일본 오사카 여행 중 어깨를 부딪히며 시비를 거는 일명 '어깨빵 빌런'을 만난 상황에서, 육은영 선생님이 이를 지혜롭고 단호하게 대처하며 참교육하는 콘텐츠입니다. 타국에서 발생할 수 있는 불쾌한 상황을 피하지 않고 현명하게 해결하는 과정을 담고 있으며, 영상 중간에는 시원한 냉각 손선풍기를 소개하는 광고가 포함되어 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 썸네일과 제목을 사용한 콘텐츠로, 실제 갈등 상황보다는 유머러스하게 연출된 상황극 위주의 영상임을 참고하여 시청하세요.</t>
-  </si>
-  <si>
-    <t>100시간 동안 세계에서 가장 오염된 도시에서 살면 생기는 일</t>
-  </si>
-  <si>
-    <t>고재영</t>
-  </si>
-  <si>
-    <t>45:14</t>
-  </si>
-  <si>
-    <t>유튜버 고재영이 세계에서 가장 오염된 도시로 알려진 곳을 직접 방문하여 100시간 동안 거주하며 겪는 생생한 현장 경험과 극한의 환경에서 느끼는 신체적, 심리적 변화를 담아낸 영상입니다. 오염된 대기질과 열악한 생활 여건 속에서 도전하는 과정을 통해 환경 오염의 심각성을 시각적으로 전달합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 썸네일과 주제를 다루고 있으므로 실제 환경 정보와 엔터테인먼트적 요소를 구분하여 시청하시기 바랍니다.</t>
-  </si>
-  <si>
-    <t>아들이랑 둘이사는 서인영 절친 싱글맘 조민아 집 최초공개 (+오해와 진실)</t>
-  </si>
-  <si>
-    <t>개과천선 서인영</t>
-  </si>
-  <si>
-    <t>29:23</t>
-  </si>
-  <si>
-    <t>서인영이 쥬얼리 멤버였던 조민아의 집을 방문하여 그동안 쌓였던 오해를 풀고 깊은 속마음을 나누는 시간을 가졌습니다. 싱글맘으로서 홀로 아들 강호를 키우고 있는 조민아의 근황과 함께, 과거 활동 시절의 추억을 회상하며 변치 않은 두 사람의 우정을 따뜻하게 보여주는 영상입니다.</t>
-  </si>
-  <si>
-    <t>연예인들의 과거 오해와 진실을 밝히는 감성적인 토크쇼를 선호하는 시청자에게 추천합니다.</t>
-  </si>
-  <si>
-    <t>일본</t>
-  </si>
-  <si>
-    <t>【元テレ東×元朝日新聞対談】新聞とテレビは終わるのか？朝日毎日読売の生存戦略／ネット時代の「有料課金」は日経一人勝ちか？／AI時代求められるのは「誰が言っているか」【下矢一良×今野忍】｜選挙ドットコム</t>
-  </si>
-  <si>
-    <t>選挙ドットコムちゃんねる</t>
-  </si>
-  <si>
-    <t>1:03:15</t>
-  </si>
-  <si>
-    <t>전직 TV도쿄 PD 하타야 카즈요시와 아사히신문 정치부 기자 콘노 시노부가 출연해 전통 미디어의 위기와 생존 전략을 논합니다. 뉴스 유료화 시대의 니케이 신문 성공 사례, AI 시대에 필수적인 정보의 신뢰성과 '누가 말하는가'의 중요성 등 미디어 산업의 미래를 심도 있게 진단합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 클릭베이트 성격이 강하므로, 제목의 자극적인 문구보다는 현업 종사자가 분석하는 미디어 시장의 구조적 변화와 신뢰성 확보 방안에 초점을 맞춰 시청하시기 바랍니다.</t>
-  </si>
-  <si>
-    <t>また韓国市場の暴落がAI関連へ波及！米軍がイランに対し空爆を実施！【6/27 米国株ニュース】</t>
-  </si>
-  <si>
-    <t>とも米国株投資チャンネル</t>
-  </si>
-  <si>
-    <t>15:19</t>
-  </si>
-  <si>
-    <t>본 영상은 한국 증시의 급락세가 AI 관련주로 확산하는 현상과 미군이 이란을 상대로 실시한 공습 소식을 다루며, 이러한 국제 정세와 시장 변동성이 미국 주식 시장에 미치는 영향을 분석합니다. 거시경제 지표와 지정학적 리스크가 투자 심리에 주는 타격을 설명하며 향후 시장 대응 전략을 제시합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 제목과 썸네일은 자극적인 이슈를 강조한 클릭베이트 요소가 포함되어 있으므로, 실제 뉴스 수치와 시장 데이터를 교차 검증하며 냉정하게 판단해야 합니다.</t>
-  </si>
-  <si>
-    <t>資産1000万円超えると人生が激変する理由</t>
-  </si>
-  <si>
-    <t>高須幹弥（高須クリニック）</t>
-  </si>
-  <si>
-    <t>20:31</t>
-  </si>
-  <si>
-    <t>타카스 미키야 원장이 자산 1,000만 엔을 넘기면 삶의 질과 정신적 여유가 달라지는 이유를 설명합니다. 소액의 자산은 심리적 안정감을 주어 대담한 의사결정을 가능하게 하며, 이것이 복리로 작용해 더 큰 자산 형성을 위한 선순환 구조를 만든다고 강조합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자산 1,000만 엔은 단순히 돈의 액수를 넘어 삶을 주도적으로 선택할 수 있는 심리적 자유의 마지노선입니다.</t>
-  </si>
-  <si>
-    <t>【元手200万→10億円】キオクシアだけを見るな！次の注目はTOPIX？／新NISA「最初の3000万円」がカギ／億を目指す4つの投資方法《上岡正明》</t>
-  </si>
-  <si>
-    <t>楽待 RAKUMACHI</t>
-  </si>
-  <si>
-    <t>53:57</t>
-  </si>
-  <si>
-    <t>자산 10억 엔을 달성한 투자자 카미오카 마사아키가 신NISA를 활용한 자산 형성 전략을 공유합니다. 3,000만 엔까지의 자산 축적이 부의 임계점이 되며, 폭락장 이후의 회복 종목 선정 및 코어-새틀라이트 전략을 통해 안정적인 투자 수익을 거두는 구체적인 방법론을 제시합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자산 증식의 첫 번째 관문인 3,000만 엔을 모으기 전까지는 위험한 투자를 피하고 NISA를 우선적으로 활용하여 기초 체력을 기르십시오.</t>
-  </si>
-  <si>
-    <t>退職後に2億円全力投資、お金が減るとこうなる【資産公開】</t>
-  </si>
-  <si>
-    <t>S&amp;P500最強伝説</t>
-  </si>
-  <si>
-    <t>37:52</t>
-  </si>
-  <si>
-    <t>은퇴 후 약 2억 엔의 자산을 S&amp;P 500에 전액 투자한 투자자의 실제 자산 변동 과정을 공개하는 영상입니다. 시장 변동성에 따라 자산이 감소하는 상황을 직접 겪으며 느낀 심리적 압박과 그럼에도 불구하고 장기 투자를 유지해야 하는 이유, 그리고 자산 운용에 대한 현실적인 경험담을 공유하여 은퇴 세대의 투자 전략을 제시합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 시장 하락기에는 자산 감소를 공포로 받아들이기보다, 장기적인 성장 가능성을 신뢰하고 흔들리지 않는 멘탈을 유지하는 것이 가장 중요합니다.</t>
-  </si>
-  <si>
-    <t>【全紹介】1〜100までの全素数の倍数判定法あなたは知っていますか？</t>
-  </si>
-  <si>
-    <t>日常でんがん</t>
-  </si>
-  <si>
-    <t>10:18</t>
-  </si>
-  <si>
-    <t>본 영상은 유튜브 채널 '일상 뎅간'의 운영자 뎅간이 출연하여 자신의 활동 배경을 소개하고 학습법에 관한 저서 '원래 바보였던 사람에 의한 바보를 위한 공부 100조'를 홍보하는 영상입니다. 과거 '하나오뎅간' 시절을 지나 현재는 수학 해설과 공부 관련 콘텐츠를 중심으로 혼자 활동하고 있으며, 시청자들에게 본인의 공부 노하우가 담긴 책을 추천하며 채널 운영 및 출연진 정보를 공유하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 수학적 지식보다는 학습법에 관한 저자 개인의 경험과 노하우를 얻고자 하는 시청자에게 적합한 홍보 중심의 영상입니다.</t>
-  </si>
-  <si>
-    <t>【受験の天王山が始まる...】前に必ず見てほしい高3向け"7月の勉強法"を解説します。</t>
-  </si>
-  <si>
-    <t>河野塾チャンネル</t>
-  </si>
-  <si>
-    <t>6:16</t>
-  </si>
-  <si>
-    <t>입시의 승부처라 불리는 7월을 맞이하는 고3 수험생을 위한 학습 전략 영상입니다. 하반기 성적 향상을 위한 학습 태도와 계획 수립의 중요성을 강조하며, 고노 주쿠가 제공하는 7월 캠페인 및 모의고사 정보를 통해 부족한 기초를 점검하고 실전 감각을 극대화할 수 있는 구체적인 가이드를 제시합니다.</t>
-  </si>
-  <si>
-    <t>⚠️입시의 성패를 좌우하는 7월은 기초를 완벽히 다지고 자신의 약점을 객관적으로 파악해 보완하는 전략적인 공부가 필수입니다.</t>
-  </si>
-  <si>
-    <t>7月で圧倒的に成績が伸びる勉強法 TOP5</t>
-  </si>
-  <si>
-    <t>ブレイクスルー佐々木</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>7:34</t>
-  </si>
-  <si>
-    <t>브레이크스루 사사키 채널의 이 영상은 7월에 성적을 극적으로 향상시킬 수 있는 5가지 학습법을 제안합니다. 여름방학은 학습 습관을 재정비하고 취약 과목을 집중 공략할 수 있는 결정적인 시기이므로, 체계적인 계획과 효율적인 공부 습관의 중요성을 강조하며 학생들에게 실질적인 전략을 제시합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 7월은 성적 역전의 골든타임이므로, 단순히 공부 시간을 늘리는 것을 넘어 자신의 수준에 맞는 정교한 학습 전략 수립이 필수입니다.</t>
-  </si>
-  <si>
-    <t>음악</t>
-  </si>
-  <si>
-    <t>「瞬間ジャーニー」 Music Video ／ TOP4(キヨ・レトルト・牛沢・ガッチマン)</t>
-  </si>
-  <si>
-    <t>キヨ。</t>
-  </si>
-  <si>
-    <t>3:49</t>
-  </si>
-  <si>
-    <t>본 영상은 인기 게임 실황자 그룹 'TOP4(키요, 레토르트, 우시자와, 갓치만)'가 발표한 곡 '순간 저니(瞬間ジャーニー)'의 공식 뮤직비디오입니다. 오렌지 레인지의 히로키가 작사, 나오토가 작곡을 맡은 곡으로, 멤버들의 개성과 우정을 담아낸 경쾌한 분위기가 특징입니다. 음악 스트리밍 서비스를 통해 음원 감상이 가능하며, 이들의 팬이라면 놓칠 수 없는 특별한 프로젝트입니다.</t>
-  </si>
-  <si>
-    <t>6월 27일 0시부터 각종 음악 스트리밍 플랫폼을 통해 정식 음원을 감상할 수 있으니 꼭 확인해보세요.</t>
-  </si>
-  <si>
-    <t>IS:SUE (イッシュ) 'come again' (Original by m-flo) Live Performance [2026.06.19 REBORN Collection 2026]</t>
-  </si>
-  <si>
-    <t>IS:SUE</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>5:04</t>
-  </si>
-  <si>
-    <t>본 영상은 걸그룹 IS:SUE가 2026년 6월 19일 'REBORN Collection 2026' 행사에서 선보인 m-flo의 히트곡 'come again' 커버 라이브 퍼포먼스 영상입니다. 멤버들의 세련된 보컬과 절도 있는 안무가 돋보이며, 원곡의 느낌을 IS:SUE만의 스타일로 재해석하여 무대 위에서 카리스마 넘치는 에너지를 발산합니다.</t>
-  </si>
-  <si>
-    <t>영상 설명란의 링크를 통해 1집 앨범 'QUARTET'과 2차 투어 정보 등 IS:SUE의 최신 활동 소식을 확인할 수 있습니다.</t>
-  </si>
-  <si>
-    <t>【マインクラフト】地下の強制労働施設で埋蔵金を探すことになりました【日常組】</t>
-  </si>
-  <si>
-    <t>日常組</t>
-  </si>
-  <si>
-    <t>1:34:58</t>
-  </si>
-  <si>
-    <t>일상조(日常組) 멤버 4명이 마인크래프트 내의 강제 노동 시설이라는 독특한 콘셉트의 맵에서 매장금을 찾기 위해 고군분투하는 내용을 담고 있습니다. 좁은 지하 환경에서 멤버들 특유의 유쾌한 입담과 상황극이 이어지며, 목표를 달성하기 위해 협동하거나 서로를 놀리는 과정에서 발생하는 에피소드가 핵심입니다.</t>
-  </si>
-  <si>
-    <t>멤버들 간의 케미스트리와 상황극이 중심이 되는 영상이므로, 시리즈의 이전 화들을 먼저 확인하면 더 깊은 재미를 느낄 수 있습니다.</t>
-  </si>
-  <si>
-    <t>【DbD】結月ゆかりの逃走劇：狂乱の宴編【VOICEROID実況】</t>
-  </si>
-  <si>
-    <t>すき焼き大好きTV</t>
-  </si>
-  <si>
-    <t>27:43</t>
-  </si>
-  <si>
-    <t>본 영상은 보이스로이드 유즈키 유카리를 활용한 데드 바이 데이라이트 실황 영상입니다. 다양한 살인마들과의 긴박한 추격전을 유머러스한 편집으로 담아냈으며, 퍼스트, 힐빌리, 트윈스, 고스트페이스 등 여러 살인마를 상대로 생존하기 위해 고군분투하는 플레이 과정을 상세히 보여줍니다.</t>
-  </si>
-  <si>
-    <t>다양한 살인마들의 특징과 그에 따른 생존자의 대처법을 간접적으로 관찰할 수 있어 초보자에게도 유익합니다.</t>
-  </si>
-  <si>
-    <t>【4人】「全員一致ゲーム＆全員不一致ゲーム」で連続目指したら地獄でした</t>
-  </si>
-  <si>
-    <t>レトルト</t>
-  </si>
-  <si>
-    <t>52:53</t>
-  </si>
-  <si>
-    <t>레토르트, 키요, 우시자와, 갓치맨 4인방이 모여 '전원 일치 게임'과 '전원 불일치 게임'에 도전하는 영상입니다. 연속 성공을 목표로 했으나 생각보다 훨씬 난항을 겪으며 아수라장이 된 현장을 담았으며, 원래는 공개되지 못할 뻔한 '보관용' 영상을 편집해 업로드한 특별한 에피소드입니다.</t>
-  </si>
-  <si>
-    <t>멤버들 간의 티키타카와 실패를 거듭하며 무너지는 광기 어린 텐션을 즐기는 것이 이 영상의 핵심 포인트입니다.</t>
-  </si>
-  <si>
-    <t>【今すぐオフ】Googleアカウントの新しいプライバシー設定と3つの変更点をわかりやすく解説！【2026年6月～】</t>
-  </si>
-  <si>
-    <t>スマホのコンシェルジュ「株式会社コアコンシェル」</t>
-  </si>
-  <si>
-    <t>2026-06-27</t>
-  </si>
-  <si>
-    <t>9:20</t>
-  </si>
-  <si>
-    <t>Google이 발표한 새로운 개인정보 보호 정책 변경 사항을 상세히 설명합니다. 특히 2026년 6월부터 적용될 주요 변경점인 미디어 저장 서비스와 검색 서비스 개인화 설정 방식을 집중 분석합니다. 사용자의 데이터 추적 방식을 이해하고, 원치 않는 기능을 직접 해제하여 개인정보를 효과적으로 보호할 수 있는 구체적인 설정 방법을 안내합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 구글 계정 설정에서 '미디어 저장' 및 '검색 서비스 개인화' 항목을 사전에 점검하여 불필요한 데이터 수집을 방지하세요.</t>
-  </si>
-  <si>
-    <t>【ボロ儲け】18万円→2万5000円！！ジャンク品から発掘したプロ専用ボードがお宝だった</t>
-  </si>
-  <si>
-    <t>おじおじの穴</t>
-  </si>
-  <si>
-    <t>32:03</t>
-  </si>
-  <si>
-    <t>본 영상은 정크품으로 판매되는 기기에서 고가의 전문가용 보드를 발견하여 큰 이득을 얻는 과정을 다루는 IT 테크 콘텐츠입니다. 저렴하게 구입한 기기를 분해 및 수리하여 가치를 재발견하는 과정을 통해 중고 전자제품의 매력과 부품 발굴의 재미를 시청자들에게 흥미롭게 전달하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 제목의 18만엔에서 2만 5천엔이라는 수치는 자극적인 클릭베이트성 요소가 강하므로, 실질적인 수익보다는 기기 분해와 수리 과정 자체를 즐기는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>【ルームツアー?】自宅にクソでかサーバーを作ったYouTuberがいるらしいので調査してきました。</t>
-  </si>
-  <si>
-    <t>TECH WORLD</t>
-  </si>
-  <si>
-    <t>25:48</t>
-  </si>
-  <si>
-    <t>IT 유튜버 'TECH WORLD'가 언차마(unchama)의 자택을 방문하여 그가 직접 구축한 대규모 가정용 서버실을 소개합니다. 일반적인 서버 운영 환경을 넘어선 전문적인 장비 구성과 구축 과정을 상세히 보여주며, 개인용 고성능 서버 환경 구축에 관심 있는 시청자들에게 실질적인 기술적 영감을 제공합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 가정 내 서버 구축 시 발열 관리와 전기료 문제에 대한 철저한 사전 설계가 필수적입니다.</t>
-  </si>
-  <si>
-    <t>溝口さんに「それ違います」と正直に伝えました</t>
-  </si>
-  <si>
-    <t>ヤマト リノ 本物</t>
-  </si>
-  <si>
-    <t>1:05:52</t>
-  </si>
-  <si>
-    <t>야마토 리노가 운영하던 10만 명 규모의 메인 채널이 해킹당해 복구가 불투명한 상황을 알리며, 시청자들에게 새로운 채널로의 구독을 간곡히 요청하는 공지 영상입니다. 기존 채널의 상실을 전하며 새로운 시작을 위한 팬들의 지지를 호소하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 채널 해킹 피해 사실을 알리며 구독을 유도하는 전형적인 긴급 공지형 클릭베이트이므로 계정 보안 관련 주의가 필요합니다.</t>
-  </si>
-  <si>
-    <t>【石川県金沢】酔った勢いで旅行したら、過去最悪の空気の旅行が仕上がりました。</t>
-  </si>
-  <si>
-    <t>うじとうえだ</t>
-  </si>
-  <si>
-    <t>2:18:07</t>
-  </si>
-  <si>
-    <t>술기운에 즉흥적으로 떠난 이시카와현 가나자와 여행에서 예민하고 결벽증이 심한 우지하라와 그를 놀리기 좋아하는 카메라맨 우에다, 친구 사카모토가 겪는 최악의 여행기를 담았습니다. 세 사람의 성격 차이로 발생하는 갈등과 긴장감이 웃음 포인트인 다큐멘터리식 여행 브이로그입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 즉흥적인 술김 여행은 동행인과의 성격 차이로 인해 최악의 분위기를 초래할 수 있다는 점을 유의하세요.</t>
+    <t>✅ Jetzt Freedom24 ausprobieren – der Broker, den ich selbst nutze: 👉  * Video gesponsert von Freed…</t>
+  </si>
+  <si>
+    <t>WM-AUS! Jetzt kommt alles raus! Ich WUSSTE ES!</t>
+  </si>
+  <si>
+    <t>10:31</t>
+  </si>
+  <si>
+    <t>✅ Jetzt Freedom24 ausprobieren – der Broker, den ich selbst nutze: 👉  * - 40.000+ Aktien &amp; 3.600 E…</t>
+  </si>
+  <si>
+    <t>JEDER muss das VOR FREITAG sehen!</t>
+  </si>
+  <si>
+    <t>15:21</t>
+  </si>
+  <si>
+    <t>𝐶𝑙𝑒𝑎𝑛𝑖𝑛𝑔 𝑎𝑛𝑑 𝐵𝑒𝑎𝑢𝑡𝑖𝑓𝑖𝑐𝑎𝑡𝑖𝑜𝑛 𝑀𝑜𝑡𝑖𝑣𝑎𝑡𝑖𝑜𝑛 #98 fg 54</t>
+  </si>
+  <si>
+    <t>The Oldies Club</t>
+  </si>
+  <si>
+    <t>1:41:49</t>
+  </si>
+  <si>
+    <t>𝐶𝑙𝑒𝑎𝑛𝑖𝑛𝑔 𝑎𝑛𝑑 𝐵𝑒𝑎𝑢𝑡𝑖𝑓𝑖𝑐𝑎𝑡𝑖𝑜𝑛 𝑀𝑜𝑡𝑖𝑣𝑎𝑡𝑖𝑜𝑛 #5858 4568 5</t>
+  </si>
+  <si>
+    <t>Asia Spa</t>
+  </si>
+  <si>
+    <t>1:39:38</t>
+  </si>
+  <si>
+    <t>연예</t>
+  </si>
+  <si>
+    <t>Muhtemel Aşk 3. Bölüm</t>
+  </si>
+  <si>
+    <t>Muhtemel Aşk</t>
+  </si>
+  <si>
+    <t>2:26:47</t>
+  </si>
+  <si>
+    <t>Muhtemel Aşk 3. Bölüm (2 Temmuz 2026) Muhtemel Aşk 3. Bölüm sahnelerini izlemek için 👉🏼 Muhtemel A…</t>
+  </si>
+  <si>
+    <t>JELENA KARLEUSA - SAD JE SVE OKEJ (PINKOVE ZVEZDE FINALE PERFORMANCE )</t>
+  </si>
+  <si>
+    <t>JELENA KARLEUŠA</t>
+  </si>
+  <si>
+    <t>3:32</t>
+  </si>
+  <si>
+    <t>Music/Lyrics: Moti Taka, Ron Biton, Maor Shtrit Lyrics: Jovana Radosavljević, Aleksandar Tomić, Je…</t>
+  </si>
+  <si>
+    <t>Argentinien – Kap Verde Highlights | Sechzehntelfinale, FIFA WM 2026 | sportstudio</t>
+  </si>
+  <si>
+    <t>sportstudio fußball</t>
+  </si>
+  <si>
+    <t>12:06</t>
+  </si>
+  <si>
+    <t>Fußball-Weltmeister Argentinien hat das WM-Märchen von Kap Verde nur mit großem Zittern beendet. D…</t>
+  </si>
+  <si>
+    <t>Lahm im großen Interview: Das Debakel, Nagelsmanns Zukunft und was alles schiefläuft  | WM 2026</t>
+  </si>
+  <si>
+    <t>kicker</t>
+  </si>
+  <si>
+    <t>20:53</t>
+  </si>
+  <si>
+    <t>"Ich war fassungslos": Lahm über das DFB-Debakel, Nagelsmann und die Zukunft | kicker-Kolumne WM-K…</t>
+  </si>
+  <si>
+    <t>Überhol-Spektakel in Silverstone! | Sprint - Highlights | Großer Preis von Großbritannien | Formel 1</t>
+  </si>
+  <si>
+    <t>Sky Sport Formel 1</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>Viel Spaß mit den Highlights vom Sprintrennen beim Großen Preis von Großbritannien auf dem Silvers…</t>
+  </si>
+  <si>
+    <t>I Tested Smartphones from Every Country</t>
+  </si>
+  <si>
+    <t>Mrwhosetheboss</t>
+  </si>
+  <si>
+    <t>24:02</t>
+  </si>
+  <si>
+    <t>Move aside Fifa - there's a new World Cup in town Go to  or use code BOSS at checkout to get 4 ext…</t>
+  </si>
+  <si>
+    <t>Why AI Tokens are so Expensive - Computerphile</t>
+  </si>
+  <si>
+    <t>Computerphile</t>
+  </si>
+  <si>
+    <t>25:22</t>
+  </si>
+  <si>
+    <t>After changes to pricing structures for LLM powered code assistants, Mike looks at how a seemingly…</t>
+  </si>
+  <si>
+    <t>Das größte Investment unserer Firmengeschichte – 1-Mio.-€-PVD-Maschine</t>
+  </si>
+  <si>
+    <t>der8auer</t>
+  </si>
+  <si>
+    <t>DSGVO konformes Hosting findest zu bei Hetzner:  -------------------------------------------------…</t>
+  </si>
+  <si>
+    <t>프랑스</t>
+  </si>
+  <si>
+    <t>Mass-Layoff Video Backfires Spectacularly</t>
+  </si>
+  <si>
+    <t>Hamish Hodder</t>
+  </si>
+  <si>
+    <t>16:04</t>
+  </si>
+  <si>
+    <t>★ Combine code 'HAMISH' with the limited time SUMMER SALE for up to 75% OFF on InvestingPro ▶︎  do…</t>
+  </si>
+  <si>
+    <t>Why I'm Investing in Private Companies Before They IPO (and how you can too)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jon Law </t>
+  </si>
+  <si>
+    <t>9:28</t>
+  </si>
+  <si>
+    <t>Take Control of Your Money and claim $5 in US Stablecoin (USA₮)! Download now at  and use the code…</t>
+  </si>
+  <si>
+    <t>PRIVATE ISLAND Renovation! Is This Even Possible?</t>
+  </si>
+  <si>
+    <t>Sanborn Construction Group</t>
+  </si>
+  <si>
+    <t>21:23</t>
+  </si>
+  <si>
+    <t>Nick and Frank are going costal today with a look at a house on a private island in need of a remo…</t>
+  </si>
+  <si>
+    <t>La Belgique a REFUSÉ de perdre... face au Sénégal</t>
+  </si>
+  <si>
+    <t>15:48</t>
+  </si>
+  <si>
+    <t>Menée 2-0, la Belgique s'impose face au Sénégal au bout de la prolongation au terme d'un scénario …</t>
+  </si>
+  <si>
+    <t>How I Work: $10M/Year Serial Entrepreneur</t>
+  </si>
+  <si>
+    <t>Starter Story</t>
+  </si>
+  <si>
+    <t>11:28</t>
+  </si>
+  <si>
+    <t>Sam Parr is a serial entrepreneur who makes over $10M/year from his companies. Everyone who follow…</t>
+  </si>
+  <si>
+    <t>6 Months Left! Here's How Not to Waste Them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ankita Sanawar </t>
+  </si>
+  <si>
+    <t>8:12</t>
+  </si>
+  <si>
+    <t>🔗‍️ 4-Week Life Reset Workbook -  If you want to change your life this is for you.I spent months w…</t>
+  </si>
+  <si>
+    <t>LE JEU DU BLUFF (Avec Anyme)</t>
+  </si>
+  <si>
+    <t>Mastu</t>
+  </si>
+  <si>
+    <t>41:17</t>
+  </si>
+  <si>
+    <t>Téléchargez REVOLUT gratuitement avec ce lien :  Vous pourrez obtenir 20 € en utilisant votre cart…</t>
+  </si>
+  <si>
+    <t>LE JUSTE POIDS ! (Avec Djilsi et Nico)</t>
+  </si>
+  <si>
+    <t>JOYCA</t>
+  </si>
+  <si>
+    <t>51:28</t>
+  </si>
+  <si>
+    <t>Merci à Saily ! Vous pouvez avoir 15% de réduction sur votre eSIM Saily avec le code JOYCA !Ça se …</t>
+  </si>
+  <si>
+    <t>DANS LA FOULE 2 (ft Maxime Biaggi, Mastu, Théodort, Byilhan &amp; Nico)</t>
+  </si>
+  <si>
+    <t>Djilsi</t>
+  </si>
+  <si>
+    <t>43:40</t>
+  </si>
+  <si>
+    <t>Inscrivez-vous sur Whatnot  et récupérez vos 15€ offerts pour tenter de gagner l’iPhone 17 ! #What…</t>
+  </si>
+  <si>
+    <t>Anas ft Abdou Gambetta - DJAZAÏRIA (Clip Officiel)</t>
+  </si>
+  <si>
+    <t>Anas Officiel</t>
+  </si>
+  <si>
+    <t>3:38</t>
+  </si>
+  <si>
+    <t>Découvre "DJAZAÏRIA" ft Abdou Gambetta :  Production : Dylexia, Redboss, Anas Enregistrement : Gab…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niska - Pow pow / Allo doudou feat. Miimii kds x Litleboy (Visualizer officiel) </t>
+  </si>
+  <si>
+    <t>Niska Officiel</t>
+  </si>
+  <si>
+    <t>3:39</t>
+  </si>
+  <si>
+    <t>Single dispo ici :  Auteur: Niska, Miimii Kds, Litleboy Beatmaker: Litleboy Clip réalisé par : Lan…</t>
+  </si>
+  <si>
+    <t>4.4.2, RK, Gradur - Papillon (Clip Officiel)</t>
+  </si>
+  <si>
+    <t>4.4.2</t>
+  </si>
+  <si>
+    <t>3:21</t>
+  </si>
+  <si>
+    <t>Découvrez le clip officiel de notre nouveau single « Papillon» disponible ici :  S'abonner à la ch…</t>
+  </si>
+  <si>
+    <t>Sony PlayStation : F*CK THE PLAYERS et puis c'est TOUT !</t>
+  </si>
+  <si>
+    <t>Conkerax</t>
+  </si>
+  <si>
+    <t>39:44</t>
+  </si>
+  <si>
+    <t>C'est la fin du disque chez PlayStation. Qui aurait cru que ce serait Sony qui nous ferait ce coup…</t>
+  </si>
+  <si>
+    <t>VOUS ME CROYEZ SI JE VOUS DIS QUE ÇA PASSE ? (Meccha Chameleon)</t>
+  </si>
+  <si>
+    <t>SQUEEZIE GAMING</t>
+  </si>
+  <si>
+    <t>49:10</t>
+  </si>
+  <si>
+    <t>💚 Mon équipe Esport, les Gentle Mates :  💜 Follow mon Twitch pour ne pas rater mon prochain live :…</t>
+  </si>
+  <si>
+    <t>The 1000 FPS Gaming PC</t>
+  </si>
+  <si>
+    <t>Linus Tech Tips</t>
+  </si>
+  <si>
+    <t>20:06</t>
+  </si>
+  <si>
+    <t>Check out the Secretlab ATLAS chair using our link:  My 1000Hz monitor is on the way, but there’s …</t>
+  </si>
+  <si>
+    <t>Je Fabrique la Switch Lite OLED ULTIME !</t>
+  </si>
+  <si>
+    <t>Millomaker</t>
+  </si>
+  <si>
+    <t>30:14</t>
+  </si>
+  <si>
+    <t>🟢UGREEN Nexode Air 65W Chargeur:  🟢UGREEN Nexode Air Slim Chargeur 65W:  🟢UGREEN MagFlow Air Batte…</t>
+  </si>
+  <si>
+    <t>On déguvine 32 bonbons avec Joyca et Matthieu et le plot twist de fin est magnifique</t>
+  </si>
+  <si>
+    <t>Mcfly et Carlito</t>
+  </si>
+  <si>
+    <t>1:24:52</t>
+  </si>
+  <si>
+    <t>10% de réduction sur vos coques et accessoires de téléphone RHINOSHIELD avec le code BISTOUGUIGUI …</t>
+  </si>
+  <si>
+    <t>ON TESTE LES PROMESSES DE PUBLICITÉS #6</t>
+  </si>
+  <si>
+    <t>Amixem</t>
+  </si>
+  <si>
+    <t>32:57</t>
+  </si>
+  <si>
+    <t>On teste de nouvelles promesses de publicités hallucinantes avec Étienne ! Essayez MyHeritage grat…</t>
+  </si>
+  <si>
+    <t>McLaren 570S : L'arme atomique, dès 150.000€</t>
+  </si>
+  <si>
+    <t>Sylvain Lyve</t>
+  </si>
+  <si>
+    <t>38:51</t>
+  </si>
+  <si>
+    <t>Merci à Saily d’avoir sponsorisé la vidéo ! Téléchargez l'application ici 👉  et obtenez 15% de réd…</t>
+  </si>
+  <si>
+    <t>라이징스타</t>
+  </si>
+  <si>
+    <t>ALPHA PEAK TATTI MOVIE REVIEW</t>
+  </si>
+  <si>
+    <t>Swan Reacts</t>
+  </si>
+  <si>
+    <t>Is it a top-secret espionage thriller or an expensive family drama with serums? 🤔 Let’s talk about…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lock Upp Season 2 Episode 6 Review | Judgement Day 🔥 Kangana Ranaut Returns as Special Guest </t>
+  </si>
+  <si>
+    <t>Aaliyas Rainbow world</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>#LockUppSeason2 #LockUpp #Episode6 #JudgementDay #KanganaRanaut #RiteishDeshmukh #FarahKhan #Netfl…</t>
   </si>
 </sst>
 </file>
@@ -1027,7 +1636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1106,16 +1715,16 @@
         <v>22</v>
       </c>
       <c r="I2" s="3">
-        <v>1265593</v>
+        <v>1271488</v>
       </c>
       <c r="J2" s="3">
-        <v>21039</v>
+        <v>21092</v>
       </c>
       <c r="K2" s="3">
-        <v>2328</v>
+        <v>2323</v>
       </c>
       <c r="L2" s="3">
-        <v>120564</v>
+        <v>117640</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>23</v>
@@ -1156,22 +1765,22 @@
         <v>30</v>
       </c>
       <c r="I3" s="3">
-        <v>175335</v>
+        <v>357904</v>
       </c>
       <c r="J3" s="3">
-        <v>2678</v>
+        <v>4679</v>
       </c>
       <c r="K3" s="3">
-        <v>998</v>
+        <v>1768</v>
       </c>
       <c r="L3" s="3">
-        <v>79732</v>
+        <v>111872</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>31</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>25</v>
@@ -1194,34 +1803,34 @@
         <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="3">
+        <v>319791</v>
+      </c>
+      <c r="J4" s="3">
+        <v>5353</v>
+      </c>
+      <c r="K4" s="3">
+        <v>497</v>
+      </c>
+      <c r="L4" s="3">
+        <v>43144</v>
+      </c>
+      <c r="M4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="3">
-        <v>294676</v>
-      </c>
-      <c r="J4" s="3">
-        <v>4967</v>
-      </c>
-      <c r="K4" s="3">
-        <v>461</v>
-      </c>
-      <c r="L4" s="3">
-        <v>42457</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="N4" s="4" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>25</v>
@@ -1238,40 +1847,40 @@
         <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="I5" s="3">
+        <v>452985</v>
+      </c>
+      <c r="J5" s="3">
+        <v>8254</v>
+      </c>
+      <c r="K5" s="3">
+        <v>463</v>
+      </c>
+      <c r="L5" s="3">
+        <v>66880</v>
+      </c>
+      <c r="M5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="3">
-        <v>757911</v>
-      </c>
-      <c r="J5" s="3">
-        <v>18669</v>
-      </c>
-      <c r="K5" s="3">
-        <v>1505</v>
-      </c>
-      <c r="L5" s="3">
-        <v>99790</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="N5" s="4" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>25</v>
@@ -1288,40 +1897,40 @@
         <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D6" s="2">
         <v>2</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="3">
+        <v>345775</v>
+      </c>
+      <c r="J6" s="3">
+        <v>5261</v>
+      </c>
+      <c r="K6" s="3">
+        <v>784</v>
+      </c>
+      <c r="L6" s="3">
+        <v>53060</v>
+      </c>
+      <c r="M6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" s="3">
-        <v>481133</v>
-      </c>
-      <c r="J6" s="3">
-        <v>8246</v>
-      </c>
-      <c r="K6" s="3">
-        <v>590</v>
-      </c>
-      <c r="L6" s="3">
-        <v>91645</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="N6" s="4" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>25</v>
@@ -1338,40 +1947,40 @@
         <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I7" s="3">
-        <v>324634</v>
+        <v>93063</v>
       </c>
       <c r="J7" s="3">
-        <v>9644</v>
+        <v>2872</v>
       </c>
       <c r="K7" s="3">
-        <v>593</v>
+        <v>76</v>
       </c>
       <c r="L7" s="3">
-        <v>73865</v>
+        <v>42961</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>25</v>
@@ -1388,40 +1997,40 @@
         <v>17</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I8" s="3">
-        <v>59339</v>
+        <v>254612</v>
       </c>
       <c r="J8" s="3">
-        <v>1595</v>
+        <v>7101</v>
       </c>
       <c r="K8" s="3">
-        <v>40</v>
+        <v>565</v>
       </c>
       <c r="L8" s="3">
-        <v>11992</v>
+        <v>45078</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>25</v>
@@ -1438,40 +2047,40 @@
         <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="I9" s="3">
-        <v>837826</v>
+        <v>21206</v>
       </c>
       <c r="J9" s="3">
-        <v>32937</v>
+        <v>1125</v>
       </c>
       <c r="K9" s="3">
-        <v>1885</v>
+        <v>324</v>
       </c>
       <c r="L9" s="3">
-        <v>276020</v>
+        <v>32304</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>25</v>
@@ -1488,40 +2097,40 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="3">
+        <v>101027</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3331</v>
+      </c>
+      <c r="K10" s="3">
+        <v>818</v>
+      </c>
+      <c r="L10" s="3">
+        <v>28504</v>
+      </c>
+      <c r="M10" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="2">
-        <v>2</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I10" s="3">
-        <v>510703</v>
-      </c>
-      <c r="J10" s="3">
-        <v>4978</v>
-      </c>
-      <c r="K10" s="3">
-        <v>660</v>
-      </c>
-      <c r="L10" s="3">
-        <v>162731</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="N10" s="4" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>25</v>
@@ -1538,40 +2147,40 @@
         <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="I11" s="3">
-        <v>177978</v>
+        <v>975586</v>
       </c>
       <c r="J11" s="3">
-        <v>11110</v>
+        <v>35559</v>
       </c>
       <c r="K11" s="3">
-        <v>1130</v>
+        <v>1941</v>
       </c>
       <c r="L11" s="3">
-        <v>128334</v>
+        <v>261294</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>25</v>
@@ -1588,40 +2197,40 @@
         <v>17</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="I12" s="3">
-        <v>715183</v>
+        <v>692347</v>
       </c>
       <c r="J12" s="3">
-        <v>6531</v>
+        <v>6007</v>
       </c>
       <c r="K12" s="3">
-        <v>2482</v>
+        <v>758</v>
       </c>
       <c r="L12" s="3">
-        <v>76551</v>
+        <v>157484</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>25</v>
@@ -1638,40 +2247,40 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="I13" s="3">
-        <v>170761</v>
+        <v>261245</v>
       </c>
       <c r="J13" s="3">
-        <v>2355</v>
+        <v>13746</v>
       </c>
       <c r="K13" s="3">
-        <v>342</v>
+        <v>1286</v>
       </c>
       <c r="L13" s="3">
-        <v>41446</v>
+        <v>120300</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>25</v>
@@ -1688,40 +2297,40 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="2">
-        <v>3</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="G14" s="2" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I14" s="3">
-        <v>468908</v>
+        <v>264528</v>
       </c>
       <c r="J14" s="3">
-        <v>19075</v>
+        <v>2983</v>
       </c>
       <c r="K14" s="3">
-        <v>2238</v>
+        <v>526</v>
       </c>
       <c r="L14" s="3">
-        <v>40769</v>
+        <v>71806</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>25</v>
@@ -1738,40 +2347,40 @@
         <v>17</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D15" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="I15" s="3">
-        <v>3243796</v>
+        <v>205651</v>
       </c>
       <c r="J15" s="3">
-        <v>70653</v>
+        <v>2756</v>
       </c>
       <c r="K15" s="3">
-        <v>11887</v>
+        <v>377</v>
       </c>
       <c r="L15" s="3">
-        <v>626741</v>
+        <v>41578</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>25</v>
@@ -1788,40 +2397,40 @@
         <v>17</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D16" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="I16" s="3">
-        <v>3498312</v>
+        <v>472048</v>
       </c>
       <c r="J16" s="3">
-        <v>43083</v>
+        <v>19199</v>
       </c>
       <c r="K16" s="3">
-        <v>5913</v>
+        <v>2269</v>
       </c>
       <c r="L16" s="3">
-        <v>396096</v>
+        <v>40676</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>25</v>
@@ -1838,40 +2447,40 @@
         <v>17</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D17" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="I17" s="3">
-        <v>1598416</v>
+        <v>3378146</v>
       </c>
       <c r="J17" s="3">
-        <v>33262</v>
+        <v>73281</v>
       </c>
       <c r="K17" s="3">
-        <v>4368</v>
+        <v>12313</v>
       </c>
       <c r="L17" s="3">
-        <v>291637</v>
+        <v>602892</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>25</v>
@@ -1885,43 +2494,43 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="D18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="I18" s="3">
-        <v>186434</v>
+        <v>3603723</v>
       </c>
       <c r="J18" s="3">
-        <v>3146</v>
+        <v>43903</v>
       </c>
       <c r="K18" s="3">
-        <v>291</v>
+        <v>5999</v>
       </c>
       <c r="L18" s="3">
-        <v>22083</v>
+        <v>388834</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>25</v>
@@ -1935,43 +2544,43 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="D19" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="I19" s="3">
-        <v>41610</v>
+        <v>1675460</v>
       </c>
       <c r="J19" s="3">
-        <v>1135</v>
+        <v>34406</v>
       </c>
       <c r="K19" s="3">
-        <v>52</v>
+        <v>4510</v>
       </c>
       <c r="L19" s="3">
-        <v>4989</v>
+        <v>281055</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>25</v>
@@ -1985,43 +2594,43 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="I20" s="3">
-        <v>505632</v>
+        <v>188893</v>
       </c>
       <c r="J20" s="3">
-        <v>6673</v>
+        <v>3189</v>
       </c>
       <c r="K20" s="3">
-        <v>1764</v>
+        <v>291</v>
       </c>
       <c r="L20" s="3">
-        <v>65370</v>
+        <v>21389</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>25</v>
@@ -2035,43 +2644,43 @@
         <v>16</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="I21" s="3">
-        <v>218511</v>
+        <v>197352</v>
       </c>
       <c r="J21" s="3">
-        <v>3496</v>
+        <v>2261</v>
       </c>
       <c r="K21" s="3">
-        <v>223</v>
+        <v>48</v>
       </c>
       <c r="L21" s="3">
-        <v>34108</v>
+        <v>33649</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>25</v>
@@ -2085,43 +2694,43 @@
         <v>16</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="2">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="2">
-        <v>3</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="I22" s="3">
-        <v>210394</v>
+        <v>230201</v>
       </c>
       <c r="J22" s="3">
-        <v>3724</v>
+        <v>3698</v>
       </c>
       <c r="K22" s="3">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L22" s="3">
-        <v>33147</v>
+        <v>33104</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>25</v>
@@ -2135,43 +2744,43 @@
         <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D23" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="I23" s="3">
-        <v>32109</v>
+        <v>145092</v>
       </c>
       <c r="J23" s="3">
-        <v>1276</v>
+        <v>1098</v>
       </c>
       <c r="K23" s="3">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="L23" s="3">
-        <v>5229</v>
+        <v>31817</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>145</v>
+        <v>24</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>25</v>
@@ -2185,43 +2794,43 @@
         <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="I24" s="3">
-        <v>26029</v>
+        <v>27740</v>
       </c>
       <c r="J24" s="3">
-        <v>650</v>
+        <v>684</v>
       </c>
       <c r="K24" s="3">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L24" s="3">
-        <v>4614</v>
+        <v>4545</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>25</v>
@@ -2235,43 +2844,43 @@
         <v>16</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D25" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="I25" s="3">
-        <v>24432</v>
+        <v>26098</v>
       </c>
       <c r="J25" s="3">
-        <v>1185</v>
+        <v>1262</v>
       </c>
       <c r="K25" s="3">
         <v>34</v>
       </c>
       <c r="L25" s="3">
-        <v>4460</v>
+        <v>4499</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>156</v>
+        <v>24</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>25</v>
@@ -2285,43 +2894,43 @@
         <v>16</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="I26" s="3">
-        <v>2176587</v>
+        <v>2329635</v>
       </c>
       <c r="J26" s="3">
-        <v>75073</v>
+        <v>76118</v>
       </c>
       <c r="K26" s="3">
-        <v>5335</v>
+        <v>5485</v>
       </c>
       <c r="L26" s="3">
-        <v>294151</v>
+        <v>296991</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>162</v>
+        <v>24</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>25</v>
@@ -2335,43 +2944,43 @@
         <v>16</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="D27" s="2">
         <v>2</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="I27" s="3">
-        <v>509342</v>
+        <v>536531</v>
       </c>
       <c r="J27" s="3">
-        <v>23328</v>
+        <v>23765</v>
       </c>
       <c r="K27" s="3">
-        <v>1814</v>
+        <v>1847</v>
       </c>
       <c r="L27" s="3">
-        <v>76477</v>
+        <v>76672</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>168</v>
+        <v>24</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>25</v>
@@ -2385,43 +2994,43 @@
         <v>16</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D28" s="2">
         <v>1</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="I28" s="3">
-        <v>789577</v>
+        <v>902046</v>
       </c>
       <c r="J28" s="3">
-        <v>26410</v>
+        <v>28752</v>
       </c>
       <c r="K28" s="3">
-        <v>1087</v>
+        <v>1152</v>
       </c>
       <c r="L28" s="3">
-        <v>225577</v>
+        <v>215618</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>173</v>
+        <v>24</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>25</v>
@@ -2435,43 +3044,43 @@
         <v>16</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D29" s="2">
         <v>2</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="I29" s="3">
-        <v>158104</v>
+        <v>279805</v>
       </c>
       <c r="J29" s="3">
-        <v>16957</v>
+        <v>23809</v>
       </c>
       <c r="K29" s="3">
-        <v>3049</v>
+        <v>3751</v>
       </c>
       <c r="L29" s="3">
-        <v>207872</v>
+        <v>208475</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>178</v>
+        <v>24</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>25</v>
@@ -2485,43 +3094,43 @@
         <v>16</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="I30" s="3">
-        <v>562171</v>
+        <v>239444</v>
       </c>
       <c r="J30" s="3">
-        <v>16050</v>
+        <v>6342</v>
       </c>
       <c r="K30" s="3">
-        <v>997</v>
+        <v>308</v>
       </c>
       <c r="L30" s="3">
-        <v>121914</v>
+        <v>116875</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>183</v>
+        <v>24</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>25</v>
@@ -2535,43 +3144,43 @@
         <v>16</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="I31" s="3">
-        <v>337825</v>
+        <v>341091</v>
       </c>
       <c r="J31" s="3">
-        <v>3694</v>
+        <v>3743</v>
       </c>
       <c r="K31" s="3">
         <v>35</v>
       </c>
       <c r="L31" s="3">
-        <v>30694</v>
+        <v>29844</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>189</v>
+        <v>24</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>25</v>
@@ -2585,43 +3194,43 @@
         <v>16</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D32" s="2">
         <v>2</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="I32" s="3">
-        <v>81928</v>
+        <v>108905</v>
       </c>
       <c r="J32" s="3">
-        <v>2447</v>
+        <v>2881</v>
       </c>
       <c r="K32" s="3">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="L32" s="3">
-        <v>24687</v>
+        <v>26133</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>194</v>
+        <v>24</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>25</v>
@@ -2635,43 +3244,43 @@
         <v>16</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D33" s="2">
         <v>3</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="I33" s="3">
-        <v>204133</v>
+        <v>208983</v>
       </c>
       <c r="J33" s="3">
-        <v>2932</v>
+        <v>2977</v>
       </c>
       <c r="K33" s="3">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L33" s="3">
-        <v>20606</v>
+        <v>20248</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>199</v>
+        <v>24</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>25</v>
@@ -2685,43 +3294,43 @@
         <v>16</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D34" s="2">
         <v>1</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="I34" s="3">
-        <v>1626677</v>
+        <v>1711380</v>
       </c>
       <c r="J34" s="3">
-        <v>27621</v>
+        <v>28450</v>
       </c>
       <c r="K34" s="3">
-        <v>12084</v>
+        <v>12294</v>
       </c>
       <c r="L34" s="3">
-        <v>426803</v>
+        <v>398581</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>204</v>
+        <v>24</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>25</v>
@@ -2735,48 +3344,3448 @@
         <v>16</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D35" s="2">
         <v>2</v>
       </c>
       <c r="E35" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I35" s="3">
+        <v>1855287</v>
+      </c>
+      <c r="J35" s="3">
+        <v>34968</v>
+      </c>
+      <c r="K35" s="3">
+        <v>3518</v>
+      </c>
+      <c r="L35" s="3">
+        <v>358805</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="2">
+        <v>1</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I36" s="3">
+        <v>2019868</v>
+      </c>
+      <c r="J36" s="3">
+        <v>49816</v>
+      </c>
+      <c r="K36" s="3">
+        <v>4882</v>
+      </c>
+      <c r="L36" s="3">
+        <v>321861</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I37" s="3">
+        <v>1159646</v>
+      </c>
+      <c r="J37" s="3">
+        <v>26099</v>
+      </c>
+      <c r="K37" s="3">
+        <v>13457</v>
+      </c>
+      <c r="L37" s="3">
+        <v>309707</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="2">
+        <v>3</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I38" s="3">
+        <v>1029552</v>
+      </c>
+      <c r="J38" s="3">
+        <v>16113</v>
+      </c>
+      <c r="K38" s="3">
+        <v>9666</v>
+      </c>
+      <c r="L38" s="3">
+        <v>193507</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="2">
+        <v>1</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I39" s="3">
+        <v>157798</v>
+      </c>
+      <c r="J39" s="3">
+        <v>15660</v>
+      </c>
+      <c r="K39" s="3">
+        <v>1862</v>
+      </c>
+      <c r="L39" s="3">
+        <v>63537</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" s="2">
+        <v>2</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I40" s="3">
+        <v>144467</v>
+      </c>
+      <c r="J40" s="3">
+        <v>8667</v>
+      </c>
+      <c r="K40" s="3">
+        <v>630</v>
+      </c>
+      <c r="L40" s="3">
+        <v>36508</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="N40" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" s="2">
+        <v>3</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I41" s="3">
+        <v>66321</v>
+      </c>
+      <c r="J41" s="3">
+        <v>4791</v>
+      </c>
+      <c r="K41" s="3">
+        <v>350</v>
+      </c>
+      <c r="L41" s="3">
+        <v>35959</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" s="2">
+        <v>1</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I42" s="3">
+        <v>3579956</v>
+      </c>
+      <c r="J42" s="3">
+        <v>98825</v>
+      </c>
+      <c r="K42" s="3">
+        <v>13688</v>
+      </c>
+      <c r="L42" s="3">
+        <v>427704</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" s="2">
+        <v>2</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="G43" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H35" s="2" t="s">
+      <c r="I43" s="3">
+        <v>3768233</v>
+      </c>
+      <c r="J43" s="3">
+        <v>103064</v>
+      </c>
+      <c r="K43" s="3">
+        <v>4920</v>
+      </c>
+      <c r="L43" s="3">
+        <v>410156</v>
+      </c>
+      <c r="M43" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="I35" s="3">
-        <v>1625460</v>
-      </c>
-      <c r="J35" s="3">
-        <v>32623</v>
-      </c>
-      <c r="K35" s="3">
-        <v>3343</v>
-      </c>
-      <c r="L35" s="3">
-        <v>365533</v>
-      </c>
-      <c r="M35" s="4" t="s">
+      <c r="N43" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" s="2">
+        <v>3</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="N35" s="4" t="s">
+      <c r="F44" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="O35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P35" s="2" t="s">
+      <c r="I44" s="3">
+        <v>3715426</v>
+      </c>
+      <c r="J44" s="3">
+        <v>80636</v>
+      </c>
+      <c r="K44" s="3">
+        <v>11630</v>
+      </c>
+      <c r="L44" s="3">
+        <v>400891</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D45" s="2">
+        <v>1</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="I45" s="3">
+        <v>7304426</v>
+      </c>
+      <c r="J45" s="3">
+        <v>224208</v>
+      </c>
+      <c r="K45" s="3">
+        <v>11359</v>
+      </c>
+      <c r="L45" s="3">
+        <v>2722753</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D46" s="2">
+        <v>2</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I46" s="3">
+        <v>2002021</v>
+      </c>
+      <c r="J46" s="3">
+        <v>109341</v>
+      </c>
+      <c r="K46" s="3">
+        <v>19816</v>
+      </c>
+      <c r="L46" s="3">
+        <v>925236</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D47" s="2">
+        <v>3</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I47" s="3">
+        <v>1342987</v>
+      </c>
+      <c r="J47" s="3">
+        <v>75821</v>
+      </c>
+      <c r="K47" s="3">
+        <v>1526</v>
+      </c>
+      <c r="L47" s="3">
+        <v>667993</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D48" s="2">
+        <v>1</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="I48" s="3">
+        <v>2595310</v>
+      </c>
+      <c r="J48" s="3">
+        <v>32909</v>
+      </c>
+      <c r="K48" s="3">
+        <v>5894</v>
+      </c>
+      <c r="L48" s="3">
+        <v>629034</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D49" s="2">
+        <v>2</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I49" s="3">
+        <v>2235954</v>
+      </c>
+      <c r="J49" s="3">
+        <v>46654</v>
+      </c>
+      <c r="K49" s="3">
+        <v>9531</v>
+      </c>
+      <c r="L49" s="3">
+        <v>490876</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D50" s="2">
+        <v>1</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I50" s="3">
+        <v>1884187</v>
+      </c>
+      <c r="J50" s="3">
+        <v>67929</v>
+      </c>
+      <c r="K50" s="3">
+        <v>2509</v>
+      </c>
+      <c r="L50" s="3">
+        <v>184902</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I51" s="3">
+        <v>1703069</v>
+      </c>
+      <c r="J51" s="3">
+        <v>44681</v>
+      </c>
+      <c r="K51" s="3">
+        <v>3954</v>
+      </c>
+      <c r="L51" s="3">
+        <v>170065</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D52" s="2">
+        <v>3</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I52" s="3">
+        <v>769356</v>
+      </c>
+      <c r="J52" s="3">
+        <v>26304</v>
+      </c>
+      <c r="K52" s="3">
+        <v>4169</v>
+      </c>
+      <c r="L52" s="3">
+        <v>149870</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53" s="2">
+        <v>1</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I53" s="3">
+        <v>131487</v>
+      </c>
+      <c r="J53" s="3">
+        <v>2730</v>
+      </c>
+      <c r="K53" s="3">
+        <v>867</v>
+      </c>
+      <c r="L53" s="3">
+        <v>37377</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D54" s="2">
+        <v>2</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="I54" s="3">
+        <v>70434</v>
+      </c>
+      <c r="J54" s="3">
+        <v>5085</v>
+      </c>
+      <c r="K54" s="3">
+        <v>621</v>
+      </c>
+      <c r="L54" s="3">
+        <v>22429</v>
+      </c>
+      <c r="M54" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="N54" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" s="2">
+        <v>3</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I55" s="3">
+        <v>93233</v>
+      </c>
+      <c r="J55" s="3">
+        <v>5231</v>
+      </c>
+      <c r="K55" s="3">
+        <v>209</v>
+      </c>
+      <c r="L55" s="3">
+        <v>19873</v>
+      </c>
+      <c r="M55" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="N55" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D56" s="2">
+        <v>1</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I56" s="3">
+        <v>128111</v>
+      </c>
+      <c r="J56" s="3">
+        <v>3090</v>
+      </c>
+      <c r="K56" s="3">
+        <v>159</v>
+      </c>
+      <c r="L56" s="3">
+        <v>17030</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D57" s="2">
+        <v>2</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I57" s="3">
+        <v>86665</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2740</v>
+      </c>
+      <c r="K57" s="3">
+        <v>236</v>
+      </c>
+      <c r="L57" s="3">
+        <v>13638</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D58" s="2">
+        <v>3</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I58" s="3">
+        <v>42907</v>
+      </c>
+      <c r="J58" s="3">
+        <v>2398</v>
+      </c>
+      <c r="K58" s="3">
+        <v>521</v>
+      </c>
+      <c r="L58" s="3">
+        <v>13102</v>
+      </c>
+      <c r="M58" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="N58" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D59" s="2">
+        <v>1</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="I59" s="3">
+        <v>7304426</v>
+      </c>
+      <c r="J59" s="3">
+        <v>224216</v>
+      </c>
+      <c r="K59" s="3">
+        <v>11359</v>
+      </c>
+      <c r="L59" s="3">
+        <v>2722786</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="N59" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D60" s="2">
+        <v>2</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I60" s="3">
+        <v>2002021</v>
+      </c>
+      <c r="J60" s="3">
+        <v>109341</v>
+      </c>
+      <c r="K60" s="3">
+        <v>19816</v>
+      </c>
+      <c r="L60" s="3">
+        <v>925236</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="N60" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D61" s="2">
+        <v>3</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I61" s="3">
+        <v>1342987</v>
+      </c>
+      <c r="J61" s="3">
+        <v>75829</v>
+      </c>
+      <c r="K61" s="3">
+        <v>1526</v>
+      </c>
+      <c r="L61" s="3">
+        <v>668029</v>
+      </c>
+      <c r="M61" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="N61" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
+      <c r="A62" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D62" s="2">
+        <v>1</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I62" s="3">
+        <v>3446389</v>
+      </c>
+      <c r="J62" s="3">
+        <v>68048</v>
+      </c>
+      <c r="K62" s="3">
+        <v>3831</v>
+      </c>
+      <c r="L62" s="3">
+        <v>1012937</v>
+      </c>
+      <c r="M62" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="N62" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16">
+      <c r="A63" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D63" s="2">
+        <v>2</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I63" s="3">
+        <v>3484302</v>
+      </c>
+      <c r="J63" s="3">
+        <v>111522</v>
+      </c>
+      <c r="K63" s="3">
+        <v>2737</v>
+      </c>
+      <c r="L63" s="3">
+        <v>465443</v>
+      </c>
+      <c r="M63" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="N63" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
+      <c r="A64" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D64" s="2">
+        <v>1</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I64" s="3">
+        <v>1738068</v>
+      </c>
+      <c r="J64" s="3">
+        <v>46992</v>
+      </c>
+      <c r="K64" s="3">
+        <v>1549</v>
+      </c>
+      <c r="L64" s="3">
+        <v>240127</v>
+      </c>
+      <c r="M64" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="N64" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16">
+      <c r="A65" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D65" s="2">
+        <v>2</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I65" s="3">
+        <v>1703069</v>
+      </c>
+      <c r="J65" s="3">
+        <v>44681</v>
+      </c>
+      <c r="K65" s="3">
+        <v>3954</v>
+      </c>
+      <c r="L65" s="3">
+        <v>170065</v>
+      </c>
+      <c r="M65" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="N65" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
+      <c r="A66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D66" s="2">
+        <v>3</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I66" s="3">
+        <v>769356</v>
+      </c>
+      <c r="J66" s="3">
+        <v>26304</v>
+      </c>
+      <c r="K66" s="3">
+        <v>4169</v>
+      </c>
+      <c r="L66" s="3">
+        <v>149870</v>
+      </c>
+      <c r="M66" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N66" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
+      <c r="A67" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D67" s="2">
+        <v>1</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="I67" s="3">
+        <v>526542</v>
+      </c>
+      <c r="J67" s="3">
+        <v>39767</v>
+      </c>
+      <c r="K67" s="3">
+        <v>6022</v>
+      </c>
+      <c r="L67" s="3">
+        <v>337807</v>
+      </c>
+      <c r="M67" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="N67" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
+      <c r="A68" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D68" s="2">
+        <v>2</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I68" s="3">
+        <v>495918</v>
+      </c>
+      <c r="J68" s="3">
+        <v>34994</v>
+      </c>
+      <c r="K68" s="3">
+        <v>4708</v>
+      </c>
+      <c r="L68" s="3">
+        <v>165417</v>
+      </c>
+      <c r="M68" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="N68" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
+      <c r="A69" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D69" s="2">
+        <v>3</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I69" s="3">
+        <v>253856</v>
+      </c>
+      <c r="J69" s="3">
+        <v>24110</v>
+      </c>
+      <c r="K69" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L69" s="3">
+        <v>115399</v>
+      </c>
+      <c r="M69" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="N69" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
+      <c r="A70" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D70" s="2">
+        <v>1</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I70" s="3">
+        <v>22596</v>
+      </c>
+      <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
+        <v>1</v>
+      </c>
+      <c r="L70" s="3">
+        <v>6408</v>
+      </c>
+      <c r="M70" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="N70" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16">
+      <c r="A71" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D71" s="2">
+        <v>2</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="I71" s="3">
+        <v>21359</v>
+      </c>
+      <c r="J71" s="3">
+        <v>252</v>
+      </c>
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3">
+        <v>4308</v>
+      </c>
+      <c r="M71" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="N71" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O71" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16">
+      <c r="A72" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D72" s="2">
+        <v>1</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="I72" s="3">
+        <v>6169674</v>
+      </c>
+      <c r="J72" s="3">
+        <v>60136</v>
+      </c>
+      <c r="K72" s="3">
+        <v>4535</v>
+      </c>
+      <c r="L72" s="3">
+        <v>974152</v>
+      </c>
+      <c r="M72" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="N72" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
+      <c r="A73" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D73" s="2">
+        <v>1</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="I73" s="3">
+        <v>481729</v>
+      </c>
+      <c r="J73" s="3">
+        <v>22566</v>
+      </c>
+      <c r="K73" s="3">
+        <v>3518</v>
+      </c>
+      <c r="L73" s="3">
+        <v>204826</v>
+      </c>
+      <c r="M73" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="N73" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
+      <c r="A74" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D74" s="2">
+        <v>1</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="I74" s="3">
+        <v>7304426</v>
+      </c>
+      <c r="J74" s="3">
+        <v>224216</v>
+      </c>
+      <c r="K74" s="3">
+        <v>11359</v>
+      </c>
+      <c r="L74" s="3">
+        <v>2722786</v>
+      </c>
+      <c r="M74" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="N74" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16">
+      <c r="A75" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D75" s="2">
+        <v>2</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I75" s="3">
+        <v>2002021</v>
+      </c>
+      <c r="J75" s="3">
+        <v>109343</v>
+      </c>
+      <c r="K75" s="3">
+        <v>19816</v>
+      </c>
+      <c r="L75" s="3">
+        <v>925242</v>
+      </c>
+      <c r="M75" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="N75" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P75" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16">
+      <c r="A76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D76" s="2">
+        <v>3</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I76" s="3">
+        <v>1342987</v>
+      </c>
+      <c r="J76" s="3">
+        <v>75829</v>
+      </c>
+      <c r="K76" s="3">
+        <v>1526</v>
+      </c>
+      <c r="L76" s="3">
+        <v>668029</v>
+      </c>
+      <c r="M76" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="N76" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16">
+      <c r="A77" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D77" s="2">
+        <v>1</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="I77" s="3">
+        <v>2124452</v>
+      </c>
+      <c r="J77" s="3">
+        <v>38688</v>
+      </c>
+      <c r="K77" s="3">
+        <v>2822</v>
+      </c>
+      <c r="L77" s="3">
+        <v>529022</v>
+      </c>
+      <c r="M77" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="N77" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P77" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16">
+      <c r="A78" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D78" s="2">
+        <v>2</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="I78" s="3">
+        <v>939436</v>
+      </c>
+      <c r="J78" s="3">
+        <v>15040</v>
+      </c>
+      <c r="K78" s="3">
+        <v>2910</v>
+      </c>
+      <c r="L78" s="3">
+        <v>141840</v>
+      </c>
+      <c r="M78" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="N78" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P78" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16">
+      <c r="A79" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D79" s="2">
+        <v>3</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I79" s="3">
+        <v>326166</v>
+      </c>
+      <c r="J79" s="3">
+        <v>7200</v>
+      </c>
+      <c r="K79" s="3">
+        <v>280</v>
+      </c>
+      <c r="L79" s="3">
+        <v>97945</v>
+      </c>
+      <c r="M79" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="N79" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P79" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16">
+      <c r="A80" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D80" s="2">
+        <v>1</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="I80" s="3">
+        <v>2432504</v>
+      </c>
+      <c r="J80" s="3">
+        <v>84624</v>
+      </c>
+      <c r="K80" s="3">
+        <v>6576</v>
+      </c>
+      <c r="L80" s="3">
+        <v>342029</v>
+      </c>
+      <c r="M80" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="N80" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16">
+      <c r="A81" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D81" s="2">
+        <v>2</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="I81" s="3">
+        <v>327547</v>
+      </c>
+      <c r="J81" s="3">
+        <v>13289</v>
+      </c>
+      <c r="K81" s="3">
+        <v>1181</v>
+      </c>
+      <c r="L81" s="3">
+        <v>83784</v>
+      </c>
+      <c r="M81" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="N81" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O81" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P81" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16">
+      <c r="A82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D82" s="2">
+        <v>3</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="I82" s="3">
+        <v>23831</v>
+      </c>
+      <c r="J82" s="3">
+        <v>3260</v>
+      </c>
+      <c r="K82" s="3">
+        <v>224</v>
+      </c>
+      <c r="L82" s="3">
+        <v>44071</v>
+      </c>
+      <c r="M82" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="N82" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P82" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16">
+      <c r="A83" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D83" s="2">
+        <v>1</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="I83" s="3">
+        <v>241559</v>
+      </c>
+      <c r="J83" s="3">
+        <v>7172</v>
+      </c>
+      <c r="K83" s="3">
+        <v>408</v>
+      </c>
+      <c r="L83" s="3">
+        <v>42051</v>
+      </c>
+      <c r="M83" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="N83" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P83" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16">
+      <c r="A84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D84" s="2">
+        <v>2</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="I84" s="3">
+        <v>160583</v>
+      </c>
+      <c r="J84" s="3">
+        <v>497</v>
+      </c>
+      <c r="K84" s="3">
+        <v>51</v>
+      </c>
+      <c r="L84" s="3">
+        <v>17189</v>
+      </c>
+      <c r="M84" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="N84" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16">
+      <c r="A85" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D85" s="2">
+        <v>3</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="I85" s="3">
+        <v>25771</v>
+      </c>
+      <c r="J85" s="3">
+        <v>1708</v>
+      </c>
+      <c r="K85" s="3">
+        <v>104</v>
+      </c>
+      <c r="L85" s="3">
+        <v>10648</v>
+      </c>
+      <c r="M85" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="N85" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16">
+      <c r="A86" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D86" s="2">
+        <v>1</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I86" s="3">
+        <v>33413</v>
+      </c>
+      <c r="J86" s="3">
+        <v>1775</v>
+      </c>
+      <c r="K86" s="3">
+        <v>341</v>
+      </c>
+      <c r="L86" s="3">
+        <v>11738</v>
+      </c>
+      <c r="M86" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="N86" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O86" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P86" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16">
+      <c r="A87" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D87" s="2">
+        <v>2</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="I87" s="3">
+        <v>30249</v>
+      </c>
+      <c r="J87" s="3">
+        <v>1187</v>
+      </c>
+      <c r="K87" s="3">
+        <v>89</v>
+      </c>
+      <c r="L87" s="3">
+        <v>6515</v>
+      </c>
+      <c r="M87" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="N87" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O87" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P87" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16">
+      <c r="A88" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D88" s="2">
+        <v>3</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="I88" s="3">
+        <v>21718</v>
+      </c>
+      <c r="J88" s="3">
+        <v>826</v>
+      </c>
+      <c r="K88" s="3">
+        <v>37</v>
+      </c>
+      <c r="L88" s="3">
+        <v>3820</v>
+      </c>
+      <c r="M88" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="N88" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O88" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P88" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16">
+      <c r="A89" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D89" s="2">
+        <v>1</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="I89" s="3">
+        <v>1182234</v>
+      </c>
+      <c r="J89" s="3">
+        <v>79136</v>
+      </c>
+      <c r="K89" s="3">
+        <v>1181</v>
+      </c>
+      <c r="L89" s="3">
+        <v>549297</v>
+      </c>
+      <c r="M89" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="N89" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O89" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P89" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16">
+      <c r="A90" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D90" s="2">
+        <v>2</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="I90" s="3">
+        <v>3083277</v>
+      </c>
+      <c r="J90" s="3">
+        <v>141958</v>
+      </c>
+      <c r="K90" s="3">
+        <v>1565</v>
+      </c>
+      <c r="L90" s="3">
+        <v>464024</v>
+      </c>
+      <c r="M90" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="N90" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O90" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P90" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16">
+      <c r="A91" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D91" s="2">
+        <v>3</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="I91" s="3">
+        <v>2810435</v>
+      </c>
+      <c r="J91" s="3">
+        <v>137022</v>
+      </c>
+      <c r="K91" s="3">
+        <v>1061</v>
+      </c>
+      <c r="L91" s="3">
+        <v>402472</v>
+      </c>
+      <c r="M91" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="N91" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O91" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P91" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16">
+      <c r="A92" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D92" s="2">
+        <v>1</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="I92" s="3">
+        <v>447562</v>
+      </c>
+      <c r="J92" s="3">
+        <v>12831</v>
+      </c>
+      <c r="K92" s="3">
+        <v>589</v>
+      </c>
+      <c r="L92" s="3">
+        <v>108416</v>
+      </c>
+      <c r="M92" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="N92" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O92" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P92" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16">
+      <c r="A93" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D93" s="2">
+        <v>2</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="I93" s="3">
+        <v>916064</v>
+      </c>
+      <c r="J93" s="3">
+        <v>25455</v>
+      </c>
+      <c r="K93" s="3">
+        <v>1256</v>
+      </c>
+      <c r="L93" s="3">
+        <v>101695</v>
+      </c>
+      <c r="M93" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="N93" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O93" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P93" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16">
+      <c r="A94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D94" s="2">
+        <v>3</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="I94" s="3">
+        <v>1007411</v>
+      </c>
+      <c r="J94" s="3">
+        <v>6204</v>
+      </c>
+      <c r="K94" s="3">
+        <v>130</v>
+      </c>
+      <c r="L94" s="3">
+        <v>78137</v>
+      </c>
+      <c r="M94" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="N94" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O94" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P94" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16">
+      <c r="A95" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D95" s="2">
+        <v>1</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I95" s="3">
+        <v>2002021</v>
+      </c>
+      <c r="J95" s="3">
+        <v>109343</v>
+      </c>
+      <c r="K95" s="3">
+        <v>19816</v>
+      </c>
+      <c r="L95" s="3">
+        <v>925242</v>
+      </c>
+      <c r="M95" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="N95" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O95" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P95" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16">
+      <c r="A96" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D96" s="2">
+        <v>2</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I96" s="3">
+        <v>40099</v>
+      </c>
+      <c r="J96" s="3">
+        <v>9110</v>
+      </c>
+      <c r="K96" s="3">
+        <v>2778</v>
+      </c>
+      <c r="L96" s="3">
+        <v>234635</v>
+      </c>
+      <c r="M96" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="N96" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O96" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P96" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16">
+      <c r="A97" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D97" s="2">
+        <v>3</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I97" s="3">
+        <v>480361</v>
+      </c>
+      <c r="J97" s="3">
+        <v>21706</v>
+      </c>
+      <c r="K97" s="3">
+        <v>177</v>
+      </c>
+      <c r="L97" s="3">
+        <v>196365</v>
+      </c>
+      <c r="M97" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="N97" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P97" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16">
+      <c r="A98" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D98" s="2">
+        <v>1</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="I98" s="3">
+        <v>770091</v>
+      </c>
+      <c r="J98" s="3">
+        <v>34012</v>
+      </c>
+      <c r="K98" s="3">
+        <v>1673</v>
+      </c>
+      <c r="L98" s="3">
+        <v>348345</v>
+      </c>
+      <c r="M98" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="N98" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O98" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P98" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
+      <c r="A99" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D99" s="2">
+        <v>2</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I99" s="3">
+        <v>1738068</v>
+      </c>
+      <c r="J99" s="3">
+        <v>46992</v>
+      </c>
+      <c r="K99" s="3">
+        <v>1549</v>
+      </c>
+      <c r="L99" s="3">
+        <v>240127</v>
+      </c>
+      <c r="M99" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="N99" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P99" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
+      <c r="A100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D100" s="2">
+        <v>3</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="I100" s="3">
+        <v>321291</v>
+      </c>
+      <c r="J100" s="3">
+        <v>13678</v>
+      </c>
+      <c r="K100" s="3">
+        <v>491</v>
+      </c>
+      <c r="L100" s="3">
+        <v>44169</v>
+      </c>
+      <c r="M100" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="N100" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O100" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P100" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
+      <c r="A101" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D101" s="2">
+        <v>1</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="I101" s="3">
+        <v>2122090</v>
+      </c>
+      <c r="J101" s="3">
+        <v>96099</v>
+      </c>
+      <c r="K101" s="3">
+        <v>2787</v>
+      </c>
+      <c r="L101" s="3">
+        <v>512486</v>
+      </c>
+      <c r="M101" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="N101" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O101" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P101" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
+      <c r="A102" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D102" s="2">
+        <v>2</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I102" s="3">
+        <v>3088148</v>
+      </c>
+      <c r="J102" s="3">
+        <v>134786</v>
+      </c>
+      <c r="K102" s="3">
+        <v>2805</v>
+      </c>
+      <c r="L102" s="3">
+        <v>469104</v>
+      </c>
+      <c r="M102" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="N102" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O102" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P102" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
+      <c r="A103" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D103" s="2">
+        <v>3</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="I103" s="3">
+        <v>806252</v>
+      </c>
+      <c r="J103" s="3">
+        <v>55567</v>
+      </c>
+      <c r="K103" s="3">
+        <v>1633</v>
+      </c>
+      <c r="L103" s="3">
+        <v>248208</v>
+      </c>
+      <c r="M103" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="N103" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O103" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P103" s="2" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2816,6 +6825,74 @@
     <hyperlink ref="O33" r:id="rId32"/>
     <hyperlink ref="O34" r:id="rId33"/>
     <hyperlink ref="O35" r:id="rId34"/>
+    <hyperlink ref="O36" r:id="rId35"/>
+    <hyperlink ref="O37" r:id="rId36"/>
+    <hyperlink ref="O38" r:id="rId37"/>
+    <hyperlink ref="O39" r:id="rId38"/>
+    <hyperlink ref="O40" r:id="rId39"/>
+    <hyperlink ref="O41" r:id="rId40"/>
+    <hyperlink ref="O42" r:id="rId41"/>
+    <hyperlink ref="O43" r:id="rId42"/>
+    <hyperlink ref="O44" r:id="rId43"/>
+    <hyperlink ref="O45" r:id="rId44"/>
+    <hyperlink ref="O46" r:id="rId45"/>
+    <hyperlink ref="O47" r:id="rId46"/>
+    <hyperlink ref="O48" r:id="rId47"/>
+    <hyperlink ref="O49" r:id="rId48"/>
+    <hyperlink ref="O50" r:id="rId49"/>
+    <hyperlink ref="O51" r:id="rId50"/>
+    <hyperlink ref="O52" r:id="rId51"/>
+    <hyperlink ref="O53" r:id="rId52"/>
+    <hyperlink ref="O54" r:id="rId53"/>
+    <hyperlink ref="O55" r:id="rId54"/>
+    <hyperlink ref="O56" r:id="rId55"/>
+    <hyperlink ref="O57" r:id="rId56"/>
+    <hyperlink ref="O58" r:id="rId57"/>
+    <hyperlink ref="O59" r:id="rId58"/>
+    <hyperlink ref="O60" r:id="rId59"/>
+    <hyperlink ref="O61" r:id="rId60"/>
+    <hyperlink ref="O62" r:id="rId61"/>
+    <hyperlink ref="O63" r:id="rId62"/>
+    <hyperlink ref="O64" r:id="rId63"/>
+    <hyperlink ref="O65" r:id="rId64"/>
+    <hyperlink ref="O66" r:id="rId65"/>
+    <hyperlink ref="O67" r:id="rId66"/>
+    <hyperlink ref="O68" r:id="rId67"/>
+    <hyperlink ref="O69" r:id="rId68"/>
+    <hyperlink ref="O70" r:id="rId69"/>
+    <hyperlink ref="O71" r:id="rId70"/>
+    <hyperlink ref="O72" r:id="rId71"/>
+    <hyperlink ref="O73" r:id="rId72"/>
+    <hyperlink ref="O74" r:id="rId73"/>
+    <hyperlink ref="O75" r:id="rId74"/>
+    <hyperlink ref="O76" r:id="rId75"/>
+    <hyperlink ref="O77" r:id="rId76"/>
+    <hyperlink ref="O78" r:id="rId77"/>
+    <hyperlink ref="O79" r:id="rId78"/>
+    <hyperlink ref="O80" r:id="rId79"/>
+    <hyperlink ref="O81" r:id="rId80"/>
+    <hyperlink ref="O82" r:id="rId81"/>
+    <hyperlink ref="O83" r:id="rId82"/>
+    <hyperlink ref="O84" r:id="rId83"/>
+    <hyperlink ref="O85" r:id="rId84"/>
+    <hyperlink ref="O86" r:id="rId85"/>
+    <hyperlink ref="O87" r:id="rId86"/>
+    <hyperlink ref="O88" r:id="rId87"/>
+    <hyperlink ref="O89" r:id="rId88"/>
+    <hyperlink ref="O90" r:id="rId89"/>
+    <hyperlink ref="O91" r:id="rId90"/>
+    <hyperlink ref="O92" r:id="rId91"/>
+    <hyperlink ref="O93" r:id="rId92"/>
+    <hyperlink ref="O94" r:id="rId93"/>
+    <hyperlink ref="O95" r:id="rId94"/>
+    <hyperlink ref="O96" r:id="rId95"/>
+    <hyperlink ref="O97" r:id="rId96"/>
+    <hyperlink ref="O98" r:id="rId97"/>
+    <hyperlink ref="O99" r:id="rId98"/>
+    <hyperlink ref="O100" r:id="rId99"/>
+    <hyperlink ref="O101" r:id="rId100"/>
+    <hyperlink ref="O102" r:id="rId101"/>
+    <hyperlink ref="O103" r:id="rId102"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2823,7 +6900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2876,7 +6953,111 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I2" s="3">
+        <v>73518</v>
+      </c>
+      <c r="J2" s="3">
+        <v>4672</v>
+      </c>
+      <c r="K2" s="3">
+        <v>1220</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="I3" s="3">
+        <v>55556</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
+        <v>17</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="O2" r:id="rId1"/>
+    <hyperlink ref="O3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>